--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM146"/>
+  <dimension ref="A1:AN146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,6 +622,11 @@
       <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>contract_url</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>winning_firm_name_zh</t>
         </is>
       </c>
     </row>
@@ -753,6 +758,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1854180</t>
         </is>
       </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>山东高速德建集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -882,6 +892,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1854432</t>
         </is>
       </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>中国电力建设集团有限公司江西电力建设分公司</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1011,6 +1026,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1834786</t>
         </is>
       </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>镇江市第二建筑工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1140,6 +1160,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1818274</t>
         </is>
       </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>镇江市第二建筑工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1269,6 +1294,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1818269</t>
         </is>
       </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>镇江市第二建筑工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1398,6 +1428,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1836455</t>
         </is>
       </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>宁波大卫医疗器械有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1527,6 +1562,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1836449</t>
         </is>
       </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>飞依诺科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1652,6 +1692,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1834577</t>
         </is>
       </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>英菲泰克有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1781,6 +1826,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802525</t>
         </is>
       </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>山东高速德建集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1910,6 +1960,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1766356</t>
         </is>
       </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>郑州润祥机械设备</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2039,6 +2094,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1733320</t>
         </is>
       </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>顾问助理</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2168,6 +2228,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1695737</t>
         </is>
       </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>中集天阳集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2297,6 +2362,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1762183</t>
         </is>
       </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>中国医药集团有限公司国际贸易分公司</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2426,6 +2496,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1667973</t>
         </is>
       </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>北京科兴中维</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2555,6 +2630,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802841</t>
         </is>
       </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>中国生物技术集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2684,6 +2764,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1716506</t>
         </is>
       </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>国药控股香港有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2813,6 +2898,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802842</t>
         </is>
       </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>中国生物技术集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2942,6 +3032,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1708728</t>
         </is>
       </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>北京科兴中维</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3071,6 +3166,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1708381</t>
         </is>
       </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>北京科兴中维</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3200,6 +3300,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1690767</t>
         </is>
       </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>北京科兴中维</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3329,6 +3434,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1640793</t>
         </is>
       </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>中国格洲坝集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3458,6 +3568,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1629574</t>
         </is>
       </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>指挥官生命值供应</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3583,6 +3698,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1623204</t>
         </is>
       </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>中国医药对外贸易总公司</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3712,6 +3832,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1620208</t>
         </is>
       </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>中国医药对外贸易总公司</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3841,6 +3966,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1630969</t>
         </is>
       </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>中国医药对外贸易总公司</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3970,6 +4100,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607231</t>
         </is>
       </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>和兴电气有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4099,6 +4234,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607230</t>
         </is>
       </c>
+      <c r="AN28" t="inlineStr">
+        <is>
+          <t>和兴电气有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4228,6 +4368,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607216</t>
         </is>
       </c>
+      <c r="AN29" t="inlineStr">
+        <is>
+          <t>和兴电气有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4357,6 +4502,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1620679</t>
         </is>
       </c>
+      <c r="AN30" t="inlineStr">
+        <is>
+          <t>深圳市桑达实业股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4486,6 +4636,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615872</t>
         </is>
       </c>
+      <c r="AN31" t="inlineStr">
+        <is>
+          <t>英科医疗（香港）有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4615,6 +4770,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615865</t>
         </is>
       </c>
+      <c r="AN32" t="inlineStr">
+        <is>
+          <t>): 上海通全对外贸易有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4744,6 +4904,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615710</t>
         </is>
       </c>
+      <c r="AN33" t="inlineStr">
+        <is>
+          <t>百事达企业</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4873,6 +5038,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1606341</t>
         </is>
       </c>
+      <c r="AN34" t="inlineStr">
+        <is>
+          <t>中山医疗科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -5002,6 +5172,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1616717</t>
         </is>
       </c>
+      <c r="AN35" t="inlineStr">
+        <is>
+          <t>威海建设集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -5131,6 +5306,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1580217</t>
         </is>
       </c>
+      <c r="AN36" t="inlineStr">
+        <is>
+          <t>深圳市迈瑞生物医药电子有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -5260,6 +5440,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1562978</t>
         </is>
       </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>四、中国建筑工程总公司</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -5389,6 +5574,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1562888</t>
         </is>
       </c>
+      <c r="AN38" t="inlineStr">
+        <is>
+          <t>联想环球科技香港有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -5518,6 +5708,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1566879</t>
         </is>
       </c>
+      <c r="AN39" t="inlineStr">
+        <is>
+          <t>个人顾问</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -5647,6 +5842,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1560811</t>
         </is>
       </c>
+      <c r="AN40" t="inlineStr">
+        <is>
+          <t>中国港湾工程有限公司；中交第二航运工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5776,6 +5976,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1560809</t>
         </is>
       </c>
+      <c r="AN41" t="inlineStr">
+        <is>
+          <t>中国港湾工程有限公司；中交第二航运工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5905,6 +6110,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1554457</t>
         </is>
       </c>
+      <c r="AN42" t="inlineStr">
+        <is>
+          <t>海尔国际商务股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6030,6 +6240,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1543474</t>
         </is>
       </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>CONSORCIO JORMAR S.A.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6155,6 +6370,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1543384</t>
         </is>
       </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>CONSORCIO JORMAR S.A.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6280,6 +6500,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1542734</t>
         </is>
       </c>
+      <c r="AN45" t="inlineStr">
+        <is>
+          <t>95543</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6409,6 +6634,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1535131</t>
         </is>
       </c>
+      <c r="AN46" t="inlineStr">
+        <is>
+          <t>先生投资（香港）有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6538,6 +6768,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1541158</t>
         </is>
       </c>
+      <c r="AN47" t="inlineStr">
+        <is>
+          <t>江苏地质工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6663,6 +6898,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1530142</t>
         </is>
       </c>
+      <c r="AN48" t="inlineStr">
+        <is>
+          <t>南瑞集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6788,6 +7028,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527391</t>
         </is>
       </c>
+      <c r="AN49" t="inlineStr">
+        <is>
+          <t>南瑞集团公司</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6913,6 +7158,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527390</t>
         </is>
       </c>
+      <c r="AN50" t="inlineStr">
+        <is>
+          <t>南瑞集团公司</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -7038,6 +7288,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527389</t>
         </is>
       </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>南瑞集团公司</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -7167,6 +7422,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1507024</t>
         </is>
       </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>深圳迈瑞生物医用电子</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -7292,6 +7552,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1327057</t>
         </is>
       </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司；中国国铁集团长春车辆厂</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -7421,6 +7686,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1325071</t>
         </is>
       </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>深圳迈瑞生物</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -7546,6 +7816,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1284880</t>
         </is>
       </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司；中国国铁集团长春车辆厂</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -7675,6 +7950,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1255975</t>
         </is>
       </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>中国成套设备进出口股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -7804,6 +8084,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1256115</t>
         </is>
       </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>中国成套设备进出口集团有限公司；威廉姆斯公司（圣卢西亚）</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7929,6 +8214,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1240081</t>
         </is>
       </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>华立作物有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -8058,6 +8348,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1224257</t>
         </is>
       </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>英石。弗朗西斯医疗；吉布德马丁有限公司；海涅</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -8183,6 +8478,11 @@
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1215237</t>
         </is>
       </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>华立集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -8310,6 +8610,11 @@
       <c r="AM61" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1211670</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>氩气；英石。方济各医疗</t>
         </is>
       </c>
     </row>
@@ -8417,6 +8722,11 @@
         </is>
       </c>
       <c r="AM62" t="inlineStr"/>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>天津优固国际贸易有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -8522,6 +8832,11 @@
         </is>
       </c>
       <c r="AM63" t="inlineStr"/>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>华大健康（香港）有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8627,6 +8942,11 @@
         </is>
       </c>
       <c r="AM64" t="inlineStr"/>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>山东瑞泰玻璃绝缘子有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8732,6 +9052,11 @@
         </is>
       </c>
       <c r="AM65" t="inlineStr"/>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>中翔混合动力科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8837,6 +9162,11 @@
         </is>
       </c>
       <c r="AM66" t="inlineStr"/>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>深圳市特发信息股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8942,6 +9272,11 @@
         </is>
       </c>
       <c r="AM67" t="inlineStr"/>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>中翔混合动力（北京）科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -9047,6 +9382,11 @@
         </is>
       </c>
       <c r="AM68" t="inlineStr"/>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>江苏双汇电力发展有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -9152,6 +9492,11 @@
         </is>
       </c>
       <c r="AM69" t="inlineStr"/>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>宇通客车股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -9257,6 +9602,11 @@
         </is>
       </c>
       <c r="AM70" t="inlineStr"/>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>中翔混合动力（北京）科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -9362,6 +9712,11 @@
         </is>
       </c>
       <c r="AM71" t="inlineStr"/>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>中国科学院战略研究联合体</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9467,6 +9822,11 @@
         </is>
       </c>
       <c r="AM72" t="inlineStr"/>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>国家电网有限公司江西分公司</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9572,6 +9932,11 @@
         </is>
       </c>
       <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>中国冶金建设有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -9677,6 +10042,11 @@
         </is>
       </c>
       <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr">
+        <is>
+          <t>中国水电有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -9782,6 +10152,11 @@
         </is>
       </c>
       <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr">
+        <is>
+          <t>河南鼎力动力设备有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9887,6 +10262,11 @@
         </is>
       </c>
       <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr">
+        <is>
+          <t>河南鼎力动力设备有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9992,6 +10372,11 @@
         </is>
       </c>
       <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>特变电工山东鲁能泰山电缆有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -10097,6 +10482,11 @@
         </is>
       </c>
       <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr">
+        <is>
+          <t>国家电网有限公司江西分公司</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -10202,6 +10592,11 @@
         </is>
       </c>
       <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr">
+        <is>
+          <t>同方威视股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -10307,6 +10702,11 @@
         </is>
       </c>
       <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr">
+        <is>
+          <t>平高集团国际工程有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -10408,6 +10808,11 @@
         </is>
       </c>
       <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr">
+        <is>
+          <t>第二十三冶金建设集团公司</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -10513,6 +10918,11 @@
         </is>
       </c>
       <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr">
+        <is>
+          <t>中航国际控股股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -10618,6 +11028,11 @@
         </is>
       </c>
       <c r="AM83" t="inlineStr"/>
+      <c r="AN83" t="inlineStr">
+        <is>
+          <t>财团渴望</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10723,6 +11138,11 @@
         </is>
       </c>
       <c r="AM84" t="inlineStr"/>
+      <c r="AN84" t="inlineStr">
+        <is>
+          <t>中国路桥工程有限责任公司与库迪普辛格基础设施公司合资</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10828,6 +11248,11 @@
         </is>
       </c>
       <c r="AM85" t="inlineStr"/>
+      <c r="AN85" t="inlineStr">
+        <is>
+          <t>中国医药集团国际联合体</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10933,6 +11358,11 @@
         </is>
       </c>
       <c r="AM86" t="inlineStr"/>
+      <c r="AN86" t="inlineStr">
+        <is>
+          <t>苏梅达集团与新晶集团合资</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -11038,6 +11468,11 @@
         </is>
       </c>
       <c r="AM87" t="inlineStr"/>
+      <c r="AN87" t="inlineStr">
+        <is>
+          <t>中国医药集团国际联合体</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -11143,6 +11578,11 @@
         </is>
       </c>
       <c r="AM88" t="inlineStr"/>
+      <c r="AN88" t="inlineStr">
+        <is>
+          <t>中国机械工程-国药国际联合体</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -11248,6 +11688,11 @@
         </is>
       </c>
       <c r="AM89" t="inlineStr"/>
+      <c r="AN89" t="inlineStr">
+        <is>
+          <t>江苏振淮建设集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -11353,6 +11798,11 @@
         </is>
       </c>
       <c r="AM90" t="inlineStr"/>
+      <c r="AN90" t="inlineStr">
+        <is>
+          <t>苏梅达集团股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -11458,6 +11908,11 @@
         </is>
       </c>
       <c r="AM91" t="inlineStr"/>
+      <c r="AN91" t="inlineStr">
+        <is>
+          <t>中国水电股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -11563,6 +12018,11 @@
         </is>
       </c>
       <c r="AM92" t="inlineStr"/>
+      <c r="AN92" t="inlineStr">
+        <is>
+          <t>中国路桥工程有限责任公司</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11668,6 +12128,11 @@
         </is>
       </c>
       <c r="AM93" t="inlineStr"/>
+      <c r="AN93" t="inlineStr">
+        <is>
+          <t>ASOCC ACCID S&amp;Z</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11773,6 +12238,11 @@
         </is>
       </c>
       <c r="AM94" t="inlineStr"/>
+      <c r="AN94" t="inlineStr">
+        <is>
+          <t>萨斯万德兹公司联合体</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11878,6 +12348,11 @@
         </is>
       </c>
       <c r="AM95" t="inlineStr"/>
+      <c r="AN95" t="inlineStr">
+        <is>
+          <t>亨通集团股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11979,6 +12454,11 @@
         </is>
       </c>
       <c r="AM96" t="inlineStr"/>
+      <c r="AN96" t="inlineStr">
+        <is>
+          <t>沃泰克有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -12084,6 +12564,11 @@
         </is>
       </c>
       <c r="AM97" t="inlineStr"/>
+      <c r="AN97" t="inlineStr">
+        <is>
+          <t>中国国电进出口有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -12185,6 +12670,11 @@
         </is>
       </c>
       <c r="AM98" t="inlineStr"/>
+      <c r="AN98" t="inlineStr">
+        <is>
+          <t>香港世界贸易中心协会</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -12290,6 +12780,11 @@
         </is>
       </c>
       <c r="AM99" t="inlineStr"/>
+      <c r="AN99" t="inlineStr">
+        <is>
+          <t>江祖中天科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12391,6 +12886,11 @@
         </is>
       </c>
       <c r="AM100" t="inlineStr"/>
+      <c r="AN100" t="inlineStr">
+        <is>
+          <t>沃泰克有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -12496,6 +12996,11 @@
         </is>
       </c>
       <c r="AM101" t="inlineStr"/>
+      <c r="AN101" t="inlineStr">
+        <is>
+          <t>人民电缆集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12597,6 +13102,11 @@
         </is>
       </c>
       <c r="AM102" t="inlineStr"/>
+      <c r="AN102" t="inlineStr">
+        <is>
+          <t>信息有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12702,6 +13212,11 @@
         </is>
       </c>
       <c r="AM103" t="inlineStr"/>
+      <c r="AN103" t="inlineStr">
+        <is>
+          <t>特变电工山东鲁能泰斯</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12807,6 +13322,11 @@
         </is>
       </c>
       <c r="AM104" t="inlineStr"/>
+      <c r="AN104" t="inlineStr">
+        <is>
+          <t>人民电缆集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12912,6 +13432,11 @@
         </is>
       </c>
       <c r="AM105" t="inlineStr"/>
+      <c r="AN105" t="inlineStr">
+        <is>
+          <t>亨通集团股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -13017,6 +13542,11 @@
         </is>
       </c>
       <c r="AM106" t="inlineStr"/>
+      <c r="AN106" t="inlineStr">
+        <is>
+          <t>中国国电布防有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -13122,6 +13652,11 @@
         </is>
       </c>
       <c r="AM107" t="inlineStr"/>
+      <c r="AN107" t="inlineStr">
+        <is>
+          <t>苏梅达集团股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -13227,6 +13762,11 @@
         </is>
       </c>
       <c r="AM108" t="inlineStr"/>
+      <c r="AN108" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -13332,6 +13872,11 @@
         </is>
       </c>
       <c r="AM109" t="inlineStr"/>
+      <c r="AN109" t="inlineStr">
+        <is>
+          <t>中国国电进出口有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -13433,6 +13978,11 @@
         </is>
       </c>
       <c r="AM110" t="inlineStr"/>
+      <c r="AN110" t="inlineStr">
+        <is>
+          <t>沃泰克有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13534,6 +14084,11 @@
         </is>
       </c>
       <c r="AM111" t="inlineStr"/>
+      <c r="AN111" t="inlineStr">
+        <is>
+          <t>沃泰克有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13639,6 +14194,11 @@
         </is>
       </c>
       <c r="AM112" t="inlineStr"/>
+      <c r="AN112" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13744,6 +14304,11 @@
         </is>
       </c>
       <c r="AM113" t="inlineStr"/>
+      <c r="AN113" t="inlineStr">
+        <is>
+          <t>正泰电气股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13849,6 +14414,11 @@
         </is>
       </c>
       <c r="AM114" t="inlineStr"/>
+      <c r="AN114" t="inlineStr">
+        <is>
+          <t>山东省电能环保股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13954,6 +14524,11 @@
         </is>
       </c>
       <c r="AM115" t="inlineStr"/>
+      <c r="AN115" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -14059,6 +14634,11 @@
         </is>
       </c>
       <c r="AM116" t="inlineStr"/>
+      <c r="AN116" t="inlineStr">
+        <is>
+          <t>中天国际有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -14164,6 +14744,11 @@
         </is>
       </c>
       <c r="AM117" t="inlineStr"/>
+      <c r="AN117" t="inlineStr">
+        <is>
+          <t>中国机械进出口集团有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -14269,6 +14854,11 @@
         </is>
       </c>
       <c r="AM118" t="inlineStr"/>
+      <c r="AN118" t="inlineStr">
+        <is>
+          <t>科技有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14374,6 +14964,11 @@
         </is>
       </c>
       <c r="AM119" t="inlineStr"/>
+      <c r="AN119" t="inlineStr">
+        <is>
+          <t>中国国电布防有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14479,6 +15074,11 @@
         </is>
       </c>
       <c r="AM120" t="inlineStr"/>
+      <c r="AN120" t="inlineStr">
+        <is>
+          <t>中国国电布防有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14580,6 +15180,11 @@
         </is>
       </c>
       <c r="AM121" t="inlineStr"/>
+      <c r="AN121" t="inlineStr">
+        <is>
+          <t>长江勘测规划设计研究有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14685,6 +15290,11 @@
         </is>
       </c>
       <c r="AM122" t="inlineStr"/>
+      <c r="AN122" t="inlineStr">
+        <is>
+          <t>泰兴凤玲音乐剧</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14790,6 +15400,11 @@
         </is>
       </c>
       <c r="AM123" t="inlineStr"/>
+      <c r="AN123" t="inlineStr">
+        <is>
+          <t>宏远建设有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14895,6 +15510,11 @@
         </is>
       </c>
       <c r="AM124" t="inlineStr"/>
+      <c r="AN124" t="inlineStr">
+        <is>
+          <t>特变电工山东鲁能泰斯</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -15000,6 +15620,11 @@
         </is>
       </c>
       <c r="AM125" t="inlineStr"/>
+      <c r="AN125" t="inlineStr">
+        <is>
+          <t>特变电工山东鲁能泰斯</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -15105,6 +15730,11 @@
         </is>
       </c>
       <c r="AM126" t="inlineStr"/>
+      <c r="AN126" t="inlineStr">
+        <is>
+          <t>正泰电气股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -15210,6 +15840,11 @@
         </is>
       </c>
       <c r="AM127" t="inlineStr"/>
+      <c r="AN127" t="inlineStr">
+        <is>
+          <t>中国水电股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15315,6 +15950,11 @@
         </is>
       </c>
       <c r="AM128" t="inlineStr"/>
+      <c r="AN128" t="inlineStr">
+        <is>
+          <t>南京大吉钢铁有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15420,6 +16060,11 @@
         </is>
       </c>
       <c r="AM129" t="inlineStr"/>
+      <c r="AN129" t="inlineStr">
+        <is>
+          <t>中国医药对外贸易总公司</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15525,6 +16170,11 @@
         </is>
       </c>
       <c r="AM130" t="inlineStr"/>
+      <c r="AN130" t="inlineStr">
+        <is>
+          <t>苏梅达集团股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15630,6 +16280,11 @@
         </is>
       </c>
       <c r="AM131" t="inlineStr"/>
+      <c r="AN131" t="inlineStr">
+        <is>
+          <t>中国医药对外贸易总公司</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15735,6 +16390,11 @@
         </is>
       </c>
       <c r="AM132" t="inlineStr"/>
+      <c r="AN132" t="inlineStr">
+        <is>
+          <t>中国水电股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15840,6 +16500,11 @@
         </is>
       </c>
       <c r="AM133" t="inlineStr"/>
+      <c r="AN133" t="inlineStr">
+        <is>
+          <t>中国机械工程-中国成套集团联合体</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15945,6 +16610,11 @@
         </is>
       </c>
       <c r="AM134" t="inlineStr"/>
+      <c r="AN134" t="inlineStr">
+        <is>
+          <t>中国机械工程-中国成套集团联合体</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -16050,6 +16720,11 @@
         </is>
       </c>
       <c r="AM135" t="inlineStr"/>
+      <c r="AN135" t="inlineStr">
+        <is>
+          <t>宏远建设有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -16155,6 +16830,11 @@
         </is>
       </c>
       <c r="AM136" t="inlineStr"/>
+      <c r="AN136" t="inlineStr">
+        <is>
+          <t>中国机械工程</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16260,6 +16940,11 @@
         </is>
       </c>
       <c r="AM137" t="inlineStr"/>
+      <c r="AN137" t="inlineStr">
+        <is>
+          <t>西安电气工程</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16365,6 +17050,11 @@
         </is>
       </c>
       <c r="AM138" t="inlineStr"/>
+      <c r="AN138" t="inlineStr">
+        <is>
+          <t>西安电气工程</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16470,6 +17160,11 @@
         </is>
       </c>
       <c r="AM139" t="inlineStr"/>
+      <c r="AN139" t="inlineStr">
+        <is>
+          <t>中国水利水电建设有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16575,6 +17270,11 @@
         </is>
       </c>
       <c r="AM140" t="inlineStr"/>
+      <c r="AN140" t="inlineStr">
+        <is>
+          <t>第一地铁线公司</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16680,6 +17380,11 @@
         </is>
       </c>
       <c r="AM141" t="inlineStr"/>
+      <c r="AN141" t="inlineStr">
+        <is>
+          <t>中国水电股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16785,6 +17490,11 @@
         </is>
       </c>
       <c r="AM142" t="inlineStr"/>
+      <c r="AN142" t="inlineStr">
+        <is>
+          <t>中国水电股份有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16890,6 +17600,11 @@
         </is>
       </c>
       <c r="AM143" t="inlineStr"/>
+      <c r="AN143" t="inlineStr">
+        <is>
+          <t>东方电气</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16995,6 +17710,11 @@
         </is>
       </c>
       <c r="AM144" t="inlineStr"/>
+      <c r="AN144" t="inlineStr">
+        <is>
+          <t>安全定制</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -17100,6 +17820,11 @@
         </is>
       </c>
       <c r="AM145" t="inlineStr"/>
+      <c r="AN145" t="inlineStr">
+        <is>
+          <t>千友信息技术（武汉）有限公司</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17205,6 +17930,11 @@
         </is>
       </c>
       <c r="AM146" t="inlineStr"/>
+      <c r="AN146" t="inlineStr">
+        <is>
+          <t>南京高速激光科技有限公司</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -712,7 +712,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
@@ -846,7 +850,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr"/>
@@ -980,7 +988,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
@@ -1114,7 +1126,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr"/>
@@ -1248,7 +1264,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
@@ -1382,7 +1402,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr"/>
@@ -1516,7 +1540,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
@@ -1646,7 +1674,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
@@ -1780,7 +1812,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr"/>
@@ -1914,7 +1950,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr"/>
@@ -2048,7 +2088,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr"/>
@@ -2182,7 +2226,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr"/>
@@ -2316,7 +2364,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr"/>
@@ -2450,7 +2502,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr"/>
@@ -2584,7 +2640,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr"/>
@@ -2718,7 +2778,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr"/>
@@ -2852,7 +2916,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
       <c r="Y18" t="inlineStr"/>
@@ -2986,7 +3054,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
       <c r="Y19" t="inlineStr"/>
@@ -3120,7 +3192,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr"/>
       <c r="Y20" t="inlineStr"/>
@@ -3254,7 +3330,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
       <c r="Y21" t="inlineStr"/>
@@ -3388,7 +3468,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W22" t="inlineStr"/>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="inlineStr"/>
@@ -3522,7 +3606,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="inlineStr"/>
@@ -3652,7 +3740,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="inlineStr"/>
@@ -3786,7 +3878,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W25" t="inlineStr"/>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="inlineStr"/>
@@ -3920,7 +4016,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W26" t="inlineStr"/>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="inlineStr"/>
@@ -4054,7 +4154,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="inlineStr"/>
@@ -4188,7 +4292,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W28" t="inlineStr"/>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="inlineStr"/>
@@ -4322,7 +4430,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="inlineStr"/>
@@ -4456,7 +4568,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr"/>
       <c r="Y30" t="inlineStr"/>
@@ -4590,7 +4706,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr"/>
       <c r="Y31" t="inlineStr"/>
@@ -4724,7 +4844,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr"/>
       <c r="Y32" t="inlineStr"/>
@@ -4858,7 +4982,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr"/>
       <c r="Y33" t="inlineStr"/>
@@ -4992,7 +5120,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr"/>
       <c r="Y34" t="inlineStr"/>
@@ -5126,7 +5258,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr"/>
@@ -5260,7 +5396,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr"/>
       <c r="Y36" t="inlineStr"/>
@@ -5394,7 +5534,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr"/>
       <c r="Y37" t="inlineStr"/>
@@ -5528,7 +5672,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W38" t="inlineStr"/>
       <c r="X38" t="inlineStr"/>
       <c r="Y38" t="inlineStr"/>
@@ -5662,7 +5810,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr"/>
       <c r="Y39" t="inlineStr"/>
@@ -5796,7 +5948,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W40" t="inlineStr"/>
       <c r="X40" t="inlineStr"/>
       <c r="Y40" t="inlineStr"/>
@@ -5930,7 +6086,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr"/>
       <c r="Y41" t="inlineStr"/>
@@ -6064,7 +6224,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr"/>
       <c r="Y42" t="inlineStr"/>
@@ -6194,7 +6358,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr"/>
       <c r="Y43" t="inlineStr"/>
@@ -6324,7 +6492,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr"/>
       <c r="Y44" t="inlineStr"/>
@@ -6454,7 +6626,11 @@
         </is>
       </c>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr"/>
       <c r="Y45" t="inlineStr"/>
@@ -6588,7 +6764,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr"/>
       <c r="Y46" t="inlineStr"/>
@@ -6722,7 +6902,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr"/>
       <c r="Y47" t="inlineStr"/>
@@ -6852,7 +7036,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr"/>
       <c r="Y48" t="inlineStr"/>
@@ -6982,7 +7170,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr"/>
       <c r="Y49" t="inlineStr"/>
@@ -7112,7 +7304,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W50" t="inlineStr"/>
       <c r="X50" t="inlineStr"/>
       <c r="Y50" t="inlineStr"/>
@@ -7242,7 +7438,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr"/>
       <c r="Y51" t="inlineStr"/>
@@ -7376,7 +7576,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr"/>
       <c r="Y52" t="inlineStr"/>
@@ -7506,7 +7710,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr"/>
       <c r="Y53" t="inlineStr"/>
@@ -7640,7 +7848,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr"/>
       <c r="Y54" t="inlineStr"/>
@@ -7770,7 +7982,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W55" t="inlineStr"/>
       <c r="X55" t="inlineStr"/>
       <c r="Y55" t="inlineStr"/>
@@ -7904,7 +8120,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W56" t="inlineStr"/>
       <c r="X56" t="inlineStr"/>
       <c r="Y56" t="inlineStr"/>
@@ -8038,7 +8258,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V57" t="inlineStr"/>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W57" t="inlineStr"/>
       <c r="X57" t="inlineStr"/>
       <c r="Y57" t="inlineStr"/>
@@ -8168,7 +8392,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V58" t="inlineStr"/>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr"/>
       <c r="Y58" t="inlineStr"/>
@@ -8302,7 +8530,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V59" t="inlineStr"/>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W59" t="inlineStr"/>
       <c r="X59" t="inlineStr"/>
       <c r="Y59" t="inlineStr"/>
@@ -8432,7 +8664,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr"/>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W60" t="inlineStr"/>
       <c r="X60" t="inlineStr"/>
       <c r="Y60" t="inlineStr"/>
@@ -8566,7 +8802,11 @@
           <t>1.0</t>
         </is>
       </c>
-      <c r="V61" t="inlineStr"/>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W61" t="inlineStr"/>
       <c r="X61" t="inlineStr"/>
       <c r="Y61" t="inlineStr"/>
@@ -8700,7 +8940,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V62" t="inlineStr"/>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W62" t="inlineStr"/>
       <c r="X62" t="inlineStr"/>
       <c r="Y62" t="inlineStr"/>
@@ -8810,7 +9054,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr"/>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W63" t="inlineStr"/>
       <c r="X63" t="inlineStr"/>
       <c r="Y63" t="inlineStr"/>
@@ -8920,7 +9168,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V64" t="inlineStr"/>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W64" t="inlineStr"/>
       <c r="X64" t="inlineStr"/>
       <c r="Y64" t="inlineStr"/>
@@ -9030,7 +9282,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V65" t="inlineStr"/>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W65" t="inlineStr"/>
       <c r="X65" t="inlineStr"/>
       <c r="Y65" t="inlineStr"/>
@@ -9140,7 +9396,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V66" t="inlineStr"/>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W66" t="inlineStr"/>
       <c r="X66" t="inlineStr"/>
       <c r="Y66" t="inlineStr"/>
@@ -9250,7 +9510,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V67" t="inlineStr"/>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W67" t="inlineStr"/>
       <c r="X67" t="inlineStr"/>
       <c r="Y67" t="inlineStr"/>
@@ -9360,7 +9624,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr"/>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W68" t="inlineStr"/>
       <c r="X68" t="inlineStr"/>
       <c r="Y68" t="inlineStr"/>
@@ -9470,7 +9738,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V69" t="inlineStr"/>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W69" t="inlineStr"/>
       <c r="X69" t="inlineStr"/>
       <c r="Y69" t="inlineStr"/>
@@ -9580,7 +9852,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr"/>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W70" t="inlineStr"/>
       <c r="X70" t="inlineStr"/>
       <c r="Y70" t="inlineStr"/>
@@ -9690,7 +9966,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V71" t="inlineStr"/>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W71" t="inlineStr"/>
       <c r="X71" t="inlineStr"/>
       <c r="Y71" t="inlineStr"/>
@@ -9800,7 +10080,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V72" t="inlineStr"/>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W72" t="inlineStr"/>
       <c r="X72" t="inlineStr"/>
       <c r="Y72" t="inlineStr"/>
@@ -9910,7 +10194,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V73" t="inlineStr"/>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W73" t="inlineStr"/>
       <c r="X73" t="inlineStr"/>
       <c r="Y73" t="inlineStr"/>
@@ -10020,7 +10308,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V74" t="inlineStr"/>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W74" t="inlineStr"/>
       <c r="X74" t="inlineStr"/>
       <c r="Y74" t="inlineStr"/>
@@ -10130,7 +10422,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V75" t="inlineStr"/>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W75" t="inlineStr"/>
       <c r="X75" t="inlineStr"/>
       <c r="Y75" t="inlineStr"/>
@@ -10240,7 +10536,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V76" t="inlineStr"/>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W76" t="inlineStr"/>
       <c r="X76" t="inlineStr"/>
       <c r="Y76" t="inlineStr"/>
@@ -10350,7 +10650,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V77" t="inlineStr"/>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr"/>
       <c r="Y77" t="inlineStr"/>
@@ -10460,7 +10764,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V78" t="inlineStr"/>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W78" t="inlineStr"/>
       <c r="X78" t="inlineStr"/>
       <c r="Y78" t="inlineStr"/>
@@ -10570,7 +10878,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V79" t="inlineStr"/>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr"/>
       <c r="Y79" t="inlineStr"/>
@@ -10680,7 +10992,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V80" t="inlineStr"/>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W80" t="inlineStr"/>
       <c r="X80" t="inlineStr"/>
       <c r="Y80" t="inlineStr"/>
@@ -10786,7 +11102,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V81" t="inlineStr"/>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr"/>
       <c r="Y81" t="inlineStr"/>
@@ -10896,7 +11216,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V82" t="inlineStr"/>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W82" t="inlineStr"/>
       <c r="X82" t="inlineStr"/>
       <c r="Y82" t="inlineStr"/>
@@ -11006,7 +11330,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V83" t="inlineStr"/>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W83" t="inlineStr"/>
       <c r="X83" t="inlineStr"/>
       <c r="Y83" t="inlineStr"/>
@@ -11116,7 +11444,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V84" t="inlineStr"/>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W84" t="inlineStr"/>
       <c r="X84" t="inlineStr"/>
       <c r="Y84" t="inlineStr"/>
@@ -11226,7 +11558,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V85" t="inlineStr"/>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W85" t="inlineStr"/>
       <c r="X85" t="inlineStr"/>
       <c r="Y85" t="inlineStr"/>
@@ -11336,7 +11672,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr"/>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W86" t="inlineStr"/>
       <c r="X86" t="inlineStr"/>
       <c r="Y86" t="inlineStr"/>
@@ -11446,7 +11786,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V87" t="inlineStr"/>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W87" t="inlineStr"/>
       <c r="X87" t="inlineStr"/>
       <c r="Y87" t="inlineStr"/>
@@ -11556,7 +11900,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V88" t="inlineStr"/>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W88" t="inlineStr"/>
       <c r="X88" t="inlineStr"/>
       <c r="Y88" t="inlineStr"/>
@@ -11666,7 +12014,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr"/>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W89" t="inlineStr"/>
       <c r="X89" t="inlineStr"/>
       <c r="Y89" t="inlineStr"/>
@@ -11776,7 +12128,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V90" t="inlineStr"/>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W90" t="inlineStr"/>
       <c r="X90" t="inlineStr"/>
       <c r="Y90" t="inlineStr"/>
@@ -11886,7 +12242,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V91" t="inlineStr"/>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W91" t="inlineStr"/>
       <c r="X91" t="inlineStr"/>
       <c r="Y91" t="inlineStr"/>
@@ -11996,7 +12356,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V92" t="inlineStr"/>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W92" t="inlineStr"/>
       <c r="X92" t="inlineStr"/>
       <c r="Y92" t="inlineStr"/>
@@ -12106,7 +12470,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V93" t="inlineStr"/>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W93" t="inlineStr"/>
       <c r="X93" t="inlineStr"/>
       <c r="Y93" t="inlineStr"/>
@@ -12216,7 +12584,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V94" t="inlineStr"/>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W94" t="inlineStr"/>
       <c r="X94" t="inlineStr"/>
       <c r="Y94" t="inlineStr"/>
@@ -12326,7 +12698,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V95" t="inlineStr"/>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W95" t="inlineStr"/>
       <c r="X95" t="inlineStr"/>
       <c r="Y95" t="inlineStr"/>
@@ -12432,7 +12808,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V96" t="inlineStr"/>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W96" t="inlineStr"/>
       <c r="X96" t="inlineStr"/>
       <c r="Y96" t="inlineStr"/>
@@ -12542,7 +12922,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V97" t="inlineStr"/>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W97" t="inlineStr"/>
       <c r="X97" t="inlineStr"/>
       <c r="Y97" t="inlineStr"/>
@@ -12648,7 +13032,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr"/>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W98" t="inlineStr"/>
       <c r="X98" t="inlineStr"/>
       <c r="Y98" t="inlineStr"/>
@@ -12758,7 +13146,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V99" t="inlineStr"/>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W99" t="inlineStr"/>
       <c r="X99" t="inlineStr"/>
       <c r="Y99" t="inlineStr"/>
@@ -12864,7 +13256,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V100" t="inlineStr"/>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W100" t="inlineStr"/>
       <c r="X100" t="inlineStr"/>
       <c r="Y100" t="inlineStr"/>
@@ -12974,7 +13370,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V101" t="inlineStr"/>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W101" t="inlineStr"/>
       <c r="X101" t="inlineStr"/>
       <c r="Y101" t="inlineStr"/>
@@ -13080,7 +13480,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V102" t="inlineStr"/>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W102" t="inlineStr"/>
       <c r="X102" t="inlineStr"/>
       <c r="Y102" t="inlineStr"/>
@@ -13190,7 +13594,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V103" t="inlineStr"/>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W103" t="inlineStr"/>
       <c r="X103" t="inlineStr"/>
       <c r="Y103" t="inlineStr"/>
@@ -13300,7 +13708,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V104" t="inlineStr"/>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W104" t="inlineStr"/>
       <c r="X104" t="inlineStr"/>
       <c r="Y104" t="inlineStr"/>
@@ -13410,7 +13822,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V105" t="inlineStr"/>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W105" t="inlineStr"/>
       <c r="X105" t="inlineStr"/>
       <c r="Y105" t="inlineStr"/>
@@ -13520,7 +13936,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V106" t="inlineStr"/>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr"/>
       <c r="X106" t="inlineStr"/>
       <c r="Y106" t="inlineStr"/>
@@ -13630,7 +14050,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V107" t="inlineStr"/>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W107" t="inlineStr"/>
       <c r="X107" t="inlineStr"/>
       <c r="Y107" t="inlineStr"/>
@@ -13740,7 +14164,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V108" t="inlineStr"/>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W108" t="inlineStr"/>
       <c r="X108" t="inlineStr"/>
       <c r="Y108" t="inlineStr"/>
@@ -13850,7 +14278,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V109" t="inlineStr"/>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W109" t="inlineStr"/>
       <c r="X109" t="inlineStr"/>
       <c r="Y109" t="inlineStr"/>
@@ -13956,7 +14388,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V110" t="inlineStr"/>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W110" t="inlineStr"/>
       <c r="X110" t="inlineStr"/>
       <c r="Y110" t="inlineStr"/>
@@ -14062,7 +14498,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V111" t="inlineStr"/>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W111" t="inlineStr"/>
       <c r="X111" t="inlineStr"/>
       <c r="Y111" t="inlineStr"/>
@@ -14172,7 +14612,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V112" t="inlineStr"/>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W112" t="inlineStr"/>
       <c r="X112" t="inlineStr"/>
       <c r="Y112" t="inlineStr"/>
@@ -14282,7 +14726,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V113" t="inlineStr"/>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W113" t="inlineStr"/>
       <c r="X113" t="inlineStr"/>
       <c r="Y113" t="inlineStr"/>
@@ -14392,7 +14840,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V114" t="inlineStr"/>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W114" t="inlineStr"/>
       <c r="X114" t="inlineStr"/>
       <c r="Y114" t="inlineStr"/>
@@ -14502,7 +14954,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V115" t="inlineStr"/>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W115" t="inlineStr"/>
       <c r="X115" t="inlineStr"/>
       <c r="Y115" t="inlineStr"/>
@@ -14612,7 +15068,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V116" t="inlineStr"/>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W116" t="inlineStr"/>
       <c r="X116" t="inlineStr"/>
       <c r="Y116" t="inlineStr"/>
@@ -14722,7 +15182,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V117" t="inlineStr"/>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W117" t="inlineStr"/>
       <c r="X117" t="inlineStr"/>
       <c r="Y117" t="inlineStr"/>
@@ -14832,7 +15296,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V118" t="inlineStr"/>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W118" t="inlineStr"/>
       <c r="X118" t="inlineStr"/>
       <c r="Y118" t="inlineStr"/>
@@ -14942,7 +15410,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V119" t="inlineStr"/>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W119" t="inlineStr"/>
       <c r="X119" t="inlineStr"/>
       <c r="Y119" t="inlineStr"/>
@@ -15052,7 +15524,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V120" t="inlineStr"/>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W120" t="inlineStr"/>
       <c r="X120" t="inlineStr"/>
       <c r="Y120" t="inlineStr"/>
@@ -15158,7 +15634,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V121" t="inlineStr"/>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W121" t="inlineStr"/>
       <c r="X121" t="inlineStr"/>
       <c r="Y121" t="inlineStr"/>
@@ -15268,7 +15748,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V122" t="inlineStr"/>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W122" t="inlineStr"/>
       <c r="X122" t="inlineStr"/>
       <c r="Y122" t="inlineStr"/>
@@ -15378,7 +15862,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V123" t="inlineStr"/>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W123" t="inlineStr"/>
       <c r="X123" t="inlineStr"/>
       <c r="Y123" t="inlineStr"/>
@@ -15488,7 +15976,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V124" t="inlineStr"/>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W124" t="inlineStr"/>
       <c r="X124" t="inlineStr"/>
       <c r="Y124" t="inlineStr"/>
@@ -15598,7 +16090,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V125" t="inlineStr"/>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W125" t="inlineStr"/>
       <c r="X125" t="inlineStr"/>
       <c r="Y125" t="inlineStr"/>
@@ -15708,7 +16204,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V126" t="inlineStr"/>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W126" t="inlineStr"/>
       <c r="X126" t="inlineStr"/>
       <c r="Y126" t="inlineStr"/>
@@ -15818,7 +16318,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V127" t="inlineStr"/>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W127" t="inlineStr"/>
       <c r="X127" t="inlineStr"/>
       <c r="Y127" t="inlineStr"/>
@@ -15928,7 +16432,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V128" t="inlineStr"/>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W128" t="inlineStr"/>
       <c r="X128" t="inlineStr"/>
       <c r="Y128" t="inlineStr"/>
@@ -16038,7 +16546,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V129" t="inlineStr"/>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W129" t="inlineStr"/>
       <c r="X129" t="inlineStr"/>
       <c r="Y129" t="inlineStr"/>
@@ -16148,7 +16660,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V130" t="inlineStr"/>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W130" t="inlineStr"/>
       <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr"/>
@@ -16258,7 +16774,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V131" t="inlineStr"/>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W131" t="inlineStr"/>
       <c r="X131" t="inlineStr"/>
       <c r="Y131" t="inlineStr"/>
@@ -16368,7 +16888,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V132" t="inlineStr"/>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W132" t="inlineStr"/>
       <c r="X132" t="inlineStr"/>
       <c r="Y132" t="inlineStr"/>
@@ -16478,7 +17002,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V133" t="inlineStr"/>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W133" t="inlineStr"/>
       <c r="X133" t="inlineStr"/>
       <c r="Y133" t="inlineStr"/>
@@ -16588,7 +17116,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V134" t="inlineStr"/>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W134" t="inlineStr"/>
       <c r="X134" t="inlineStr"/>
       <c r="Y134" t="inlineStr"/>
@@ -16698,7 +17230,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V135" t="inlineStr"/>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W135" t="inlineStr"/>
       <c r="X135" t="inlineStr"/>
       <c r="Y135" t="inlineStr"/>
@@ -16808,7 +17344,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V136" t="inlineStr"/>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W136" t="inlineStr"/>
       <c r="X136" t="inlineStr"/>
       <c r="Y136" t="inlineStr"/>
@@ -16918,7 +17458,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V137" t="inlineStr"/>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W137" t="inlineStr"/>
       <c r="X137" t="inlineStr"/>
       <c r="Y137" t="inlineStr"/>
@@ -17028,7 +17572,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V138" t="inlineStr"/>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W138" t="inlineStr"/>
       <c r="X138" t="inlineStr"/>
       <c r="Y138" t="inlineStr"/>
@@ -17138,7 +17686,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V139" t="inlineStr"/>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W139" t="inlineStr"/>
       <c r="X139" t="inlineStr"/>
       <c r="Y139" t="inlineStr"/>
@@ -17248,7 +17800,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V140" t="inlineStr"/>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W140" t="inlineStr"/>
       <c r="X140" t="inlineStr"/>
       <c r="Y140" t="inlineStr"/>
@@ -17358,7 +17914,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V141" t="inlineStr"/>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W141" t="inlineStr"/>
       <c r="X141" t="inlineStr"/>
       <c r="Y141" t="inlineStr"/>
@@ -17468,7 +18028,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V142" t="inlineStr"/>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W142" t="inlineStr"/>
       <c r="X142" t="inlineStr"/>
       <c r="Y142" t="inlineStr"/>
@@ -17578,7 +18142,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V143" t="inlineStr"/>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W143" t="inlineStr"/>
       <c r="X143" t="inlineStr"/>
       <c r="Y143" t="inlineStr"/>
@@ -17688,7 +18256,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr"/>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W144" t="inlineStr"/>
       <c r="X144" t="inlineStr"/>
       <c r="Y144" t="inlineStr"/>
@@ -17798,7 +18370,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V145" t="inlineStr"/>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W145" t="inlineStr"/>
       <c r="X145" t="inlineStr"/>
       <c r="Y145" t="inlineStr"/>
@@ -17908,7 +18484,11 @@
           <t>True</t>
         </is>
       </c>
-      <c r="V146" t="inlineStr"/>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="W146" t="inlineStr"/>
       <c r="X146" t="inlineStr"/>
       <c r="Y146" t="inlineStr"/>

--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -1681,7 +1681,7 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Agriculture &amp; Rural Dev.</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Agriculture &amp; Rural Dev.</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">

--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -746,7 +746,11 @@
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -889,7 +893,11 @@
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1032,7 +1040,11 @@
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1175,7 +1187,11 @@
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ5" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1318,7 +1334,11 @@
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ6" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1461,7 +1481,11 @@
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ7" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1604,7 +1628,11 @@
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1743,7 +1771,11 @@
       </c>
       <c r="AG9" t="inlineStr"/>
       <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ9" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -1886,7 +1918,11 @@
       </c>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ10" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2029,7 +2065,11 @@
       </c>
       <c r="AG11" t="inlineStr"/>
       <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2172,7 +2212,11 @@
       </c>
       <c r="AG12" t="inlineStr"/>
       <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2315,7 +2359,11 @@
       </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ13" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2458,7 +2506,11 @@
       </c>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2601,7 +2653,11 @@
       </c>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ15" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2744,7 +2800,11 @@
       </c>
       <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ16" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2887,7 +2947,11 @@
       </c>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ17" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3030,7 +3094,11 @@
       </c>
       <c r="AG18" t="inlineStr"/>
       <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3173,7 +3241,11 @@
       </c>
       <c r="AG19" t="inlineStr"/>
       <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ19" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3316,7 +3388,11 @@
       </c>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3459,7 +3535,11 @@
       </c>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3602,7 +3682,11 @@
       </c>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ22" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3745,7 +3829,11 @@
       </c>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -3884,7 +3972,11 @@
       </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4027,7 +4119,11 @@
       </c>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ25" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4170,7 +4266,11 @@
       </c>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4313,7 +4413,11 @@
       </c>
       <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4456,7 +4560,11 @@
       </c>
       <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ28" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4599,7 +4707,11 @@
       </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ29" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4742,7 +4854,11 @@
       </c>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ30" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -4885,7 +5001,11 @@
       </c>
       <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ31" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5028,7 +5148,11 @@
       </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ32" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5171,7 +5295,11 @@
       </c>
       <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5314,7 +5442,11 @@
       </c>
       <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ34" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5457,7 +5589,11 @@
       </c>
       <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ35" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5600,7 +5736,11 @@
       </c>
       <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ36" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5743,7 +5883,11 @@
       </c>
       <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ37" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -5886,7 +6030,11 @@
       </c>
       <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ38" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6025,7 +6173,11 @@
       </c>
       <c r="AG39" t="inlineStr"/>
       <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ39" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6168,7 +6320,11 @@
       </c>
       <c r="AG40" t="inlineStr"/>
       <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ40" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6311,7 +6467,11 @@
       </c>
       <c r="AG41" t="inlineStr"/>
       <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ41" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6454,7 +6614,11 @@
       </c>
       <c r="AG42" t="inlineStr"/>
       <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ42" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6593,7 +6757,11 @@
       </c>
       <c r="AG43" t="inlineStr"/>
       <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ43" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6732,7 +6900,11 @@
       </c>
       <c r="AG44" t="inlineStr"/>
       <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ44" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -6873,7 +7045,7 @@
       <c r="AH45" t="inlineStr"/>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr"/>
@@ -7014,7 +7186,11 @@
       </c>
       <c r="AG46" t="inlineStr"/>
       <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ46" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7157,7 +7333,11 @@
       </c>
       <c r="AG47" t="inlineStr"/>
       <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
+      <c r="AI47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ47" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7296,7 +7476,11 @@
       </c>
       <c r="AG48" t="inlineStr"/>
       <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ48" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7435,7 +7619,11 @@
       </c>
       <c r="AG49" t="inlineStr"/>
       <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ49" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7574,7 +7762,11 @@
       </c>
       <c r="AG50" t="inlineStr"/>
       <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ50" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7713,7 +7905,11 @@
       </c>
       <c r="AG51" t="inlineStr"/>
       <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ51" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7856,7 +8052,11 @@
       </c>
       <c r="AG52" t="inlineStr"/>
       <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ52" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -7995,7 +8195,11 @@
       </c>
       <c r="AG53" t="inlineStr"/>
       <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ53" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8138,7 +8342,11 @@
       </c>
       <c r="AG54" t="inlineStr"/>
       <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ54" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8277,7 +8485,11 @@
       </c>
       <c r="AG55" t="inlineStr"/>
       <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ55" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8420,7 +8632,11 @@
       </c>
       <c r="AG56" t="inlineStr"/>
       <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ56" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8563,7 +8779,11 @@
       </c>
       <c r="AG57" t="inlineStr"/>
       <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ57" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8702,7 +8922,11 @@
       </c>
       <c r="AG58" t="inlineStr"/>
       <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ58" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8845,7 +9069,11 @@
       </c>
       <c r="AG59" t="inlineStr"/>
       <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ59" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -8984,7 +9212,11 @@
       </c>
       <c r="AG60" t="inlineStr"/>
       <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ60" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9127,7 +9359,11 @@
       </c>
       <c r="AG61" t="inlineStr"/>
       <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr"/>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="AJ61" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -9266,7 +9502,11 @@
       <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="inlineStr"/>
       <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr"/>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ62" t="inlineStr"/>
       <c r="AK62" t="inlineStr"/>
       <c r="AL62" t="inlineStr"/>
@@ -9385,7 +9625,11 @@
       <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="inlineStr"/>
       <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr"/>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ63" t="inlineStr"/>
       <c r="AK63" t="inlineStr"/>
       <c r="AL63" t="inlineStr"/>
@@ -9504,7 +9748,11 @@
       <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="inlineStr"/>
       <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr"/>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ64" t="inlineStr"/>
       <c r="AK64" t="inlineStr"/>
       <c r="AL64" t="inlineStr"/>
@@ -9623,7 +9871,11 @@
       <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="inlineStr"/>
       <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr"/>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ65" t="inlineStr"/>
       <c r="AK65" t="inlineStr"/>
       <c r="AL65" t="inlineStr"/>
@@ -9742,7 +9994,11 @@
       <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="inlineStr"/>
       <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr"/>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ66" t="inlineStr"/>
       <c r="AK66" t="inlineStr"/>
       <c r="AL66" t="inlineStr"/>
@@ -9861,7 +10117,11 @@
       <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="inlineStr"/>
       <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr"/>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ67" t="inlineStr"/>
       <c r="AK67" t="inlineStr"/>
       <c r="AL67" t="inlineStr"/>
@@ -9980,7 +10240,11 @@
       <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="inlineStr"/>
       <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr"/>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ68" t="inlineStr"/>
       <c r="AK68" t="inlineStr"/>
       <c r="AL68" t="inlineStr"/>
@@ -10099,7 +10363,11 @@
       <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="inlineStr"/>
       <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr"/>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ69" t="inlineStr"/>
       <c r="AK69" t="inlineStr"/>
       <c r="AL69" t="inlineStr"/>
@@ -10218,7 +10486,11 @@
       <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="inlineStr"/>
       <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr"/>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ70" t="inlineStr"/>
       <c r="AK70" t="inlineStr"/>
       <c r="AL70" t="inlineStr"/>
@@ -10337,7 +10609,11 @@
       <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="inlineStr"/>
       <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr"/>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ71" t="inlineStr"/>
       <c r="AK71" t="inlineStr"/>
       <c r="AL71" t="inlineStr"/>
@@ -10456,7 +10732,11 @@
       <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="inlineStr"/>
       <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr"/>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ72" t="inlineStr"/>
       <c r="AK72" t="inlineStr"/>
       <c r="AL72" t="inlineStr"/>
@@ -10575,7 +10855,11 @@
       <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="inlineStr"/>
       <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ73" t="inlineStr"/>
       <c r="AK73" t="inlineStr"/>
       <c r="AL73" t="inlineStr"/>
@@ -10694,7 +10978,11 @@
       <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="inlineStr"/>
       <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ74" t="inlineStr"/>
       <c r="AK74" t="inlineStr"/>
       <c r="AL74" t="inlineStr"/>
@@ -10813,7 +11101,11 @@
       <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="inlineStr"/>
       <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ75" t="inlineStr"/>
       <c r="AK75" t="inlineStr"/>
       <c r="AL75" t="inlineStr"/>
@@ -10932,7 +11224,11 @@
       <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="inlineStr"/>
       <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ76" t="inlineStr"/>
       <c r="AK76" t="inlineStr"/>
       <c r="AL76" t="inlineStr"/>
@@ -11051,7 +11347,11 @@
       <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="inlineStr"/>
       <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ77" t="inlineStr"/>
       <c r="AK77" t="inlineStr"/>
       <c r="AL77" t="inlineStr"/>
@@ -11170,7 +11470,11 @@
       <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="inlineStr"/>
       <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ78" t="inlineStr"/>
       <c r="AK78" t="inlineStr"/>
       <c r="AL78" t="inlineStr"/>
@@ -11289,7 +11593,11 @@
       <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="inlineStr"/>
       <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ79" t="inlineStr"/>
       <c r="AK79" t="inlineStr"/>
       <c r="AL79" t="inlineStr"/>
@@ -11408,7 +11716,11 @@
       <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="inlineStr"/>
       <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ80" t="inlineStr"/>
       <c r="AK80" t="inlineStr"/>
       <c r="AL80" t="inlineStr"/>
@@ -11523,7 +11835,11 @@
       <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="inlineStr"/>
       <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ81" t="inlineStr"/>
       <c r="AK81" t="inlineStr"/>
       <c r="AL81" t="inlineStr"/>
@@ -11642,7 +11958,11 @@
       <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="inlineStr"/>
       <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ82" t="inlineStr"/>
       <c r="AK82" t="inlineStr"/>
       <c r="AL82" t="inlineStr"/>
@@ -11761,7 +12081,11 @@
       <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="inlineStr"/>
       <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr"/>
+      <c r="AI83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ83" t="inlineStr"/>
       <c r="AK83" t="inlineStr"/>
       <c r="AL83" t="inlineStr"/>
@@ -11880,7 +12204,11 @@
       <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="inlineStr"/>
       <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr"/>
+      <c r="AI84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ84" t="inlineStr"/>
       <c r="AK84" t="inlineStr"/>
       <c r="AL84" t="inlineStr"/>
@@ -11999,7 +12327,11 @@
       <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="inlineStr"/>
       <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr"/>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ85" t="inlineStr"/>
       <c r="AK85" t="inlineStr"/>
       <c r="AL85" t="inlineStr"/>
@@ -12118,7 +12450,11 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="inlineStr"/>
       <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr"/>
+      <c r="AI86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ86" t="inlineStr"/>
       <c r="AK86" t="inlineStr"/>
       <c r="AL86" t="inlineStr"/>
@@ -12237,7 +12573,11 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="inlineStr"/>
       <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr"/>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ87" t="inlineStr"/>
       <c r="AK87" t="inlineStr"/>
       <c r="AL87" t="inlineStr"/>
@@ -12356,7 +12696,11 @@
       <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="inlineStr"/>
       <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr"/>
+      <c r="AI88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ88" t="inlineStr"/>
       <c r="AK88" t="inlineStr"/>
       <c r="AL88" t="inlineStr"/>
@@ -12475,7 +12819,11 @@
       <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="inlineStr"/>
       <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr"/>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ89" t="inlineStr"/>
       <c r="AK89" t="inlineStr"/>
       <c r="AL89" t="inlineStr"/>
@@ -12594,7 +12942,11 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="inlineStr"/>
       <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr"/>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ90" t="inlineStr"/>
       <c r="AK90" t="inlineStr"/>
       <c r="AL90" t="inlineStr"/>
@@ -12713,7 +13065,11 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="inlineStr"/>
       <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr"/>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ91" t="inlineStr"/>
       <c r="AK91" t="inlineStr"/>
       <c r="AL91" t="inlineStr"/>
@@ -12832,7 +13188,11 @@
       <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="inlineStr"/>
       <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr"/>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ92" t="inlineStr"/>
       <c r="AK92" t="inlineStr"/>
       <c r="AL92" t="inlineStr"/>
@@ -12951,7 +13311,11 @@
       <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="inlineStr"/>
       <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr"/>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ93" t="inlineStr"/>
       <c r="AK93" t="inlineStr"/>
       <c r="AL93" t="inlineStr"/>
@@ -13070,7 +13434,11 @@
       <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="inlineStr"/>
       <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr"/>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ94" t="inlineStr"/>
       <c r="AK94" t="inlineStr"/>
       <c r="AL94" t="inlineStr"/>
@@ -13189,7 +13557,11 @@
       <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="inlineStr"/>
       <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr"/>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ95" t="inlineStr"/>
       <c r="AK95" t="inlineStr"/>
       <c r="AL95" t="inlineStr"/>
@@ -13304,7 +13676,11 @@
       <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="inlineStr"/>
       <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr"/>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ96" t="inlineStr"/>
       <c r="AK96" t="inlineStr"/>
       <c r="AL96" t="inlineStr"/>
@@ -13423,7 +13799,11 @@
       <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="inlineStr"/>
       <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr"/>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ97" t="inlineStr"/>
       <c r="AK97" t="inlineStr"/>
       <c r="AL97" t="inlineStr"/>
@@ -13538,7 +13918,11 @@
       <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="inlineStr"/>
       <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr"/>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ98" t="inlineStr"/>
       <c r="AK98" t="inlineStr"/>
       <c r="AL98" t="inlineStr"/>
@@ -13657,7 +14041,11 @@
       <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="inlineStr"/>
       <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr"/>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ99" t="inlineStr"/>
       <c r="AK99" t="inlineStr"/>
       <c r="AL99" t="inlineStr"/>
@@ -13772,7 +14160,11 @@
       <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="inlineStr"/>
       <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr"/>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ100" t="inlineStr"/>
       <c r="AK100" t="inlineStr"/>
       <c r="AL100" t="inlineStr"/>
@@ -13891,7 +14283,11 @@
       <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="inlineStr"/>
       <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr"/>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ101" t="inlineStr"/>
       <c r="AK101" t="inlineStr"/>
       <c r="AL101" t="inlineStr"/>
@@ -14006,7 +14402,11 @@
       <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="inlineStr"/>
       <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr"/>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ102" t="inlineStr"/>
       <c r="AK102" t="inlineStr"/>
       <c r="AL102" t="inlineStr"/>
@@ -14125,7 +14525,11 @@
       <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="inlineStr"/>
       <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr"/>
+      <c r="AI103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ103" t="inlineStr"/>
       <c r="AK103" t="inlineStr"/>
       <c r="AL103" t="inlineStr"/>
@@ -14244,7 +14648,11 @@
       <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="inlineStr"/>
       <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr"/>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ104" t="inlineStr"/>
       <c r="AK104" t="inlineStr"/>
       <c r="AL104" t="inlineStr"/>
@@ -14363,7 +14771,11 @@
       <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="inlineStr"/>
       <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr"/>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ105" t="inlineStr"/>
       <c r="AK105" t="inlineStr"/>
       <c r="AL105" t="inlineStr"/>
@@ -14482,7 +14894,11 @@
       <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="inlineStr"/>
       <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr"/>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ106" t="inlineStr"/>
       <c r="AK106" t="inlineStr"/>
       <c r="AL106" t="inlineStr"/>
@@ -14601,7 +15017,11 @@
       <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="inlineStr"/>
       <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr"/>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ107" t="inlineStr"/>
       <c r="AK107" t="inlineStr"/>
       <c r="AL107" t="inlineStr"/>
@@ -14720,7 +15140,11 @@
       <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="inlineStr"/>
       <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr"/>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ108" t="inlineStr"/>
       <c r="AK108" t="inlineStr"/>
       <c r="AL108" t="inlineStr"/>
@@ -14839,7 +15263,11 @@
       <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="inlineStr"/>
       <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr"/>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ109" t="inlineStr"/>
       <c r="AK109" t="inlineStr"/>
       <c r="AL109" t="inlineStr"/>
@@ -14954,7 +15382,11 @@
       <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="inlineStr"/>
       <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr"/>
+      <c r="AI110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ110" t="inlineStr"/>
       <c r="AK110" t="inlineStr"/>
       <c r="AL110" t="inlineStr"/>
@@ -15069,7 +15501,11 @@
       <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="inlineStr"/>
       <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr"/>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ111" t="inlineStr"/>
       <c r="AK111" t="inlineStr"/>
       <c r="AL111" t="inlineStr"/>
@@ -15188,7 +15624,11 @@
       <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="inlineStr"/>
       <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ112" t="inlineStr"/>
       <c r="AK112" t="inlineStr"/>
       <c r="AL112" t="inlineStr"/>
@@ -15307,7 +15747,11 @@
       <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="inlineStr"/>
       <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ113" t="inlineStr"/>
       <c r="AK113" t="inlineStr"/>
       <c r="AL113" t="inlineStr"/>
@@ -15426,7 +15870,11 @@
       <c r="AF114" t="inlineStr"/>
       <c r="AG114" t="inlineStr"/>
       <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ114" t="inlineStr"/>
       <c r="AK114" t="inlineStr"/>
       <c r="AL114" t="inlineStr"/>
@@ -15545,7 +15993,11 @@
       <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="inlineStr"/>
       <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ115" t="inlineStr"/>
       <c r="AK115" t="inlineStr"/>
       <c r="AL115" t="inlineStr"/>
@@ -15664,7 +16116,11 @@
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="inlineStr"/>
       <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ116" t="inlineStr"/>
       <c r="AK116" t="inlineStr"/>
       <c r="AL116" t="inlineStr"/>
@@ -15783,7 +16239,11 @@
       <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="inlineStr"/>
       <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ117" t="inlineStr"/>
       <c r="AK117" t="inlineStr"/>
       <c r="AL117" t="inlineStr"/>
@@ -15902,7 +16362,11 @@
       <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="inlineStr"/>
       <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ118" t="inlineStr"/>
       <c r="AK118" t="inlineStr"/>
       <c r="AL118" t="inlineStr"/>
@@ -16021,7 +16485,11 @@
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="inlineStr"/>
       <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ119" t="inlineStr"/>
       <c r="AK119" t="inlineStr"/>
       <c r="AL119" t="inlineStr"/>
@@ -16140,7 +16608,11 @@
       <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="inlineStr"/>
       <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ120" t="inlineStr"/>
       <c r="AK120" t="inlineStr"/>
       <c r="AL120" t="inlineStr"/>
@@ -16255,7 +16727,11 @@
       <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="inlineStr"/>
       <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ121" t="inlineStr"/>
       <c r="AK121" t="inlineStr"/>
       <c r="AL121" t="inlineStr"/>
@@ -16374,7 +16850,11 @@
       <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="inlineStr"/>
       <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ122" t="inlineStr"/>
       <c r="AK122" t="inlineStr"/>
       <c r="AL122" t="inlineStr"/>
@@ -16493,7 +16973,11 @@
       <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="inlineStr"/>
       <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ123" t="inlineStr"/>
       <c r="AK123" t="inlineStr"/>
       <c r="AL123" t="inlineStr"/>
@@ -16612,7 +17096,11 @@
       <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="inlineStr"/>
       <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ124" t="inlineStr"/>
       <c r="AK124" t="inlineStr"/>
       <c r="AL124" t="inlineStr"/>
@@ -16731,7 +17219,11 @@
       <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="inlineStr"/>
       <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ125" t="inlineStr"/>
       <c r="AK125" t="inlineStr"/>
       <c r="AL125" t="inlineStr"/>
@@ -16850,7 +17342,11 @@
       <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="inlineStr"/>
       <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ126" t="inlineStr"/>
       <c r="AK126" t="inlineStr"/>
       <c r="AL126" t="inlineStr"/>
@@ -16969,7 +17465,11 @@
       <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="inlineStr"/>
       <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ127" t="inlineStr"/>
       <c r="AK127" t="inlineStr"/>
       <c r="AL127" t="inlineStr"/>
@@ -17088,7 +17588,11 @@
       <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="inlineStr"/>
       <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ128" t="inlineStr"/>
       <c r="AK128" t="inlineStr"/>
       <c r="AL128" t="inlineStr"/>
@@ -17207,7 +17711,11 @@
       <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="inlineStr"/>
       <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ129" t="inlineStr"/>
       <c r="AK129" t="inlineStr"/>
       <c r="AL129" t="inlineStr"/>
@@ -17326,7 +17834,11 @@
       <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="inlineStr"/>
       <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ130" t="inlineStr"/>
       <c r="AK130" t="inlineStr"/>
       <c r="AL130" t="inlineStr"/>
@@ -17445,7 +17957,11 @@
       <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="inlineStr"/>
       <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ131" t="inlineStr"/>
       <c r="AK131" t="inlineStr"/>
       <c r="AL131" t="inlineStr"/>
@@ -17564,7 +18080,11 @@
       <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="inlineStr"/>
       <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ132" t="inlineStr"/>
       <c r="AK132" t="inlineStr"/>
       <c r="AL132" t="inlineStr"/>
@@ -17683,7 +18203,11 @@
       <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="inlineStr"/>
       <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ133" t="inlineStr"/>
       <c r="AK133" t="inlineStr"/>
       <c r="AL133" t="inlineStr"/>
@@ -17802,7 +18326,11 @@
       <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="inlineStr"/>
       <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ134" t="inlineStr"/>
       <c r="AK134" t="inlineStr"/>
       <c r="AL134" t="inlineStr"/>
@@ -17921,7 +18449,11 @@
       <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="inlineStr"/>
       <c r="AH135" t="inlineStr"/>
-      <c r="AI135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ135" t="inlineStr"/>
       <c r="AK135" t="inlineStr"/>
       <c r="AL135" t="inlineStr"/>
@@ -18040,7 +18572,11 @@
       <c r="AF136" t="inlineStr"/>
       <c r="AG136" t="inlineStr"/>
       <c r="AH136" t="inlineStr"/>
-      <c r="AI136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ136" t="inlineStr"/>
       <c r="AK136" t="inlineStr"/>
       <c r="AL136" t="inlineStr"/>
@@ -18159,7 +18695,11 @@
       <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="inlineStr"/>
       <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ137" t="inlineStr"/>
       <c r="AK137" t="inlineStr"/>
       <c r="AL137" t="inlineStr"/>
@@ -18278,7 +18818,11 @@
       <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="inlineStr"/>
       <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ138" t="inlineStr"/>
       <c r="AK138" t="inlineStr"/>
       <c r="AL138" t="inlineStr"/>
@@ -18397,7 +18941,11 @@
       <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="inlineStr"/>
       <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ139" t="inlineStr"/>
       <c r="AK139" t="inlineStr"/>
       <c r="AL139" t="inlineStr"/>
@@ -18516,7 +19064,11 @@
       <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="inlineStr"/>
       <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ140" t="inlineStr"/>
       <c r="AK140" t="inlineStr"/>
       <c r="AL140" t="inlineStr"/>
@@ -18635,7 +19187,11 @@
       <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="inlineStr"/>
       <c r="AH141" t="inlineStr"/>
-      <c r="AI141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ141" t="inlineStr"/>
       <c r="AK141" t="inlineStr"/>
       <c r="AL141" t="inlineStr"/>
@@ -18754,7 +19310,11 @@
       <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="inlineStr"/>
       <c r="AH142" t="inlineStr"/>
-      <c r="AI142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ142" t="inlineStr"/>
       <c r="AK142" t="inlineStr"/>
       <c r="AL142" t="inlineStr"/>
@@ -18873,7 +19433,11 @@
       <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="inlineStr"/>
       <c r="AH143" t="inlineStr"/>
-      <c r="AI143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ143" t="inlineStr"/>
       <c r="AK143" t="inlineStr"/>
       <c r="AL143" t="inlineStr"/>
@@ -18992,7 +19556,11 @@
       <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="inlineStr"/>
       <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ144" t="inlineStr"/>
       <c r="AK144" t="inlineStr"/>
       <c r="AL144" t="inlineStr"/>
@@ -19111,7 +19679,11 @@
       <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="inlineStr"/>
       <c r="AH145" t="inlineStr"/>
-      <c r="AI145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ145" t="inlineStr"/>
       <c r="AK145" t="inlineStr"/>
       <c r="AL145" t="inlineStr"/>
@@ -19230,7 +19802,11 @@
       <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="inlineStr"/>
       <c r="AH146" t="inlineStr"/>
-      <c r="AI146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AJ146" t="inlineStr"/>
       <c r="AK146" t="inlineStr"/>
       <c r="AL146" t="inlineStr"/>

--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -6322,7 +6322,7 @@
       <c r="AH40" t="inlineStr"/>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -6469,7 +6469,7 @@
       <c r="AH41" t="inlineStr"/>
       <c r="AI41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ41" t="inlineStr">
@@ -8197,7 +8197,7 @@
       <c r="AH53" t="inlineStr"/>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -8487,7 +8487,7 @@
       <c r="AH55" t="inlineStr"/>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">

--- a/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
+++ b/docs/data/worldbank_idb_aiddata_cdb_merged.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO146"/>
+  <dimension ref="A1:AG146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,85 +551,45 @@
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>number_of_bidders</t>
+          <t>financing_linked_to_bid</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>if_single_bidder</t>
+          <t>financing_source_chinese</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>bidder_country_lowest_price</t>
+          <t>joint_venture</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>bidder_lowest_price</t>
+          <t>firm_registered_locally</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>bidder_country</t>
+          <t>record_id</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>bidder_price_currency</t>
+          <t>awarded_date</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>bidder_price</t>
+          <t>bid_reference_no</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>procurement_method</t>
+          <t>project_name</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>financing_linked_to_bid</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>financing_source_chinese</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
-        <is>
-          <t>joint_venture</t>
-        </is>
-      </c>
-      <c r="AJ1" s="1" t="inlineStr">
-        <is>
-          <t>firm_registered_locally</t>
-        </is>
-      </c>
-      <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>record_id</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>awarded_date</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>bid_reference_no</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>project_name</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>contract_url</t>
         </is>
@@ -734,49 +694,37 @@
       </c>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1854180</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>GY-MOE-400689-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1854180</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2025-07-31</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>GY-MOE-400689-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
           <t>Guyana Strengthening Human Capital through Education Project</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1854180</t>
         </is>
@@ -881,49 +829,37 @@
       </c>
       <c r="Y3" t="inlineStr"/>
       <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1854432</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2025-06-23</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>GY-MOE-465937-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1854432</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>2025-06-23</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>GY-MOE-465937-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
           <t>Guyana Strengthening Human Capital through Education Project</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1854432</t>
         </is>
@@ -1028,49 +964,37 @@
       </c>
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1834786</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>SX-NRPB-387097-CW-RFB-1</t>
+        </is>
+      </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1834786</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>SX-NRPB-387097-CW-RFB-1</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
           <t>Sint Maarten Emergency Recovery Project I</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1834786</t>
         </is>
@@ -1175,49 +1099,37 @@
       </c>
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1818274</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>SX-NRPB-386118-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1818274</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>SX-NRPB-386118-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
           <t>Sint Maarten Emergency Recovery Project I</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AG5" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1818274</t>
         </is>
@@ -1322,49 +1234,37 @@
       </c>
       <c r="Y6" t="inlineStr"/>
       <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1818269</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>SX-NRPB-386924-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>1818269</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>2025-01-06</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>SX-NRPB-386924-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
           <t>Sint Maarten Emergency Recovery Project I</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AG6" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1818269</t>
         </is>
@@ -1469,49 +1369,37 @@
       </c>
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1836455</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>AR-MSAL-200462-GO-RFB</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>1836455</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>2024-05-28</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>AR-MSAL-200462-GO-RFB</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
           <t>Supporting Effective Universal Health Coverage in Argentina</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1836455</t>
         </is>
@@ -1616,49 +1504,37 @@
       </c>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1836449</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2024-05-20</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>AR-MSAL-200462-GO-RFB</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1836449</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>2024-05-20</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>AR-MSAL-200462-GO-RFB</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
           <t>Supporting Effective Universal Health Coverage in Argentina</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1836449</t>
         </is>
@@ -1759,49 +1635,37 @@
       </c>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1834577</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>2024-01-04</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>GD-MOIID-380067-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1834577</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>2024-01-04</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>GD-MOIID-380067-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
           <t>Unleashing the Blue Economy of the Caribbean (UBEC)</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1834577</t>
         </is>
@@ -1906,49 +1770,37 @@
       </c>
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1802525</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>2023-11-14</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>GESIP/RFB/CW-1</t>
+        </is>
+      </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>1802525</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>2023-11-14</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>GESIP/RFB/CW-1</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
           <t>Guyana Education Sector Improvement Project</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802525</t>
         </is>
@@ -2053,49 +1905,37 @@
       </c>
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1766356</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>2023-09-25</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>JM-MICAF-368948-GO-RFQ</t>
+        </is>
+      </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Request for Quotations</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>1766356</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>2023-09-25</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>JM-MICAF-368948-GO-RFQ</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
           <t>Promoting Community-based Climate Resilience in the Fisheries Sector</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AG11" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1766356</t>
         </is>
@@ -2200,49 +2040,37 @@
       </c>
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1733320</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2022-06-27</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>SVGCARDTP-C-CQS-2</t>
+        </is>
+      </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>Consultant Qualification  Selection</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1733320</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>2022-06-27</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>SVGCARDTP-C-CQS-2</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
           <t>Caribbean Digital Transformation Project</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AG12" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1733320</t>
         </is>
@@ -2347,49 +2175,37 @@
       </c>
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1695737</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>2022-04-20</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>SX-PJIAE-236385-GO-RFB</t>
+        </is>
+      </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>1695737</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>2022-04-20</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>SX-PJIAE-236385-GO-RFB</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
           <t>Sint Maarten Airport Terminal Reconstruction Project</t>
         </is>
       </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AG13" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1695737</t>
         </is>
@@ -2494,49 +2310,37 @@
       </c>
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1762183</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2021-12-20</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>GY-G-COVID FTO-278205-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>1762183</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>2021-12-20</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>GY-G-COVID FTO-278205-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
           <t>Guyana COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO14" t="inlineStr">
+      <c r="AG14" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1762183</t>
         </is>
@@ -2641,49 +2445,37 @@
       </c>
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1667973</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>2021-07-31</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>EC-MPH-DFA-246372-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>1667973</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>2021-07-31</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>EC-MPH-DFA-246372-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
           <t>Ecuador COVID-19 Emergency Response and Vaccination Project</t>
         </is>
       </c>
-      <c r="AO15" t="inlineStr">
+      <c r="AG15" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1667973</t>
         </is>
@@ -2788,49 +2580,37 @@
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
-      <c r="AA16" t="inlineStr"/>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>1802841</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2021-06-29</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>TT-MOH-348518-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>1802841</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>2021-06-29</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>TT-MOH-348518-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
           <t>Republic of Trinidad and Tobago: COVID-19 EMERGENCY RESPONSE PROJECT</t>
         </is>
       </c>
-      <c r="AO16" t="inlineStr">
+      <c r="AG16" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802841</t>
         </is>
@@ -2935,49 +2715,37 @@
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
-      <c r="AA17" t="inlineStr"/>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>1716506</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>2021-06-09</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>GY-G-COVID FTO-296098-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>1716506</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>2021-06-09</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>GY-G-COVID FTO-296098-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
           <t>Guyana COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO17" t="inlineStr">
+      <c r="AG17" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1716506</t>
         </is>
@@ -3082,49 +2850,37 @@
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
-      <c r="AA18" t="inlineStr"/>
-      <c r="AB18" t="inlineStr"/>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1802842</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2021-06-06</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>TT-MOH-348548-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>1802842</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>2021-06-06</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>TT-MOH-348548-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
           <t>Republic of Trinidad and Tobago: COVID-19 EMERGENCY RESPONSE PROJECT</t>
         </is>
       </c>
-      <c r="AO18" t="inlineStr">
+      <c r="AG18" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1802842</t>
         </is>
@@ -3229,49 +2985,37 @@
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
-      <c r="AA19" t="inlineStr"/>
-      <c r="AB19" t="inlineStr"/>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1708728</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>RECOVID-88-DIR-GO</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>1708728</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>RECOVID-88-DIR-GO</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
           <t>El Salvador COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO19" t="inlineStr">
+      <c r="AG19" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1708728</t>
         </is>
@@ -3376,49 +3120,37 @@
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr"/>
-      <c r="AA20" t="inlineStr"/>
-      <c r="AB20" t="inlineStr"/>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1708381</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>RECOVID-91-DIR-GO</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>1708381</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>RECOVID-91-DIR-GO</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
           <t>El Salvador COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO20" t="inlineStr">
+      <c r="AG20" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1708381</t>
         </is>
@@ -3523,49 +3255,37 @@
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr"/>
-      <c r="AA21" t="inlineStr"/>
-      <c r="AB21" t="inlineStr"/>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>1690767</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>2021-03-10</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>RECOVID-49-DIR-GO-2</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>1690767</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>2021-03-10</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>RECOVID-49-DIR-GO-2</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
           <t>El Salvador COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO21" t="inlineStr">
+      <c r="AG21" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1690767</t>
         </is>
@@ -3670,49 +3390,37 @@
       </c>
       <c r="Y22" t="inlineStr"/>
       <c r="Z22" t="inlineStr"/>
-      <c r="AA22" t="inlineStr"/>
-      <c r="AB22" t="inlineStr"/>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>1640793</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>2020-12-29</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>PE-COPESCO-157324-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>1640793</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>2020-12-29</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>PE-COPESCO-157324-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
           <t>Cusco Transport Improvement Project</t>
         </is>
       </c>
-      <c r="AO22" t="inlineStr">
+      <c r="AG22" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1640793</t>
         </is>
@@ -3817,49 +3525,37 @@
       </c>
       <c r="Y23" t="inlineStr"/>
       <c r="Z23" t="inlineStr"/>
-      <c r="AA23" t="inlineStr"/>
-      <c r="AB23" t="inlineStr"/>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>1629574</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>2020-08-10</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>EC-MPH-DFA-186835-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>1629574</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>2020-08-10</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>EC-MPH-DFA-186835-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
           <t>Ecuador COVID-19 Emergency Response and Vaccination Project</t>
         </is>
       </c>
-      <c r="AO23" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1629574</t>
         </is>
@@ -3960,49 +3656,37 @@
       </c>
       <c r="Y24" t="inlineStr"/>
       <c r="Z24" t="inlineStr"/>
-      <c r="AA24" t="inlineStr"/>
-      <c r="AB24" t="inlineStr"/>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>1623204</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>2020-06-24</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>HN-INVEST-H-174944-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>1623204</t>
-        </is>
-      </c>
-      <c r="AL24" t="inlineStr">
-        <is>
-          <t>2020-06-24</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>HN-INVEST-H-174944-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
           <t>Honduras COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO24" t="inlineStr">
+      <c r="AG24" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1623204</t>
         </is>
@@ -4107,49 +3791,37 @@
       </c>
       <c r="Y25" t="inlineStr"/>
       <c r="Z25" t="inlineStr"/>
-      <c r="AA25" t="inlineStr"/>
-      <c r="AB25" t="inlineStr"/>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>1620208</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>GO-DIR-12-2020</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>1620208</t>
-        </is>
-      </c>
-      <c r="AL25" t="inlineStr">
-        <is>
-          <t>2020-06-15</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>GO-DIR-12-2020</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
           <t>AR: COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO25" t="inlineStr">
+      <c r="AG25" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1620208</t>
         </is>
@@ -4254,49 +3926,37 @@
       </c>
       <c r="Y26" t="inlineStr"/>
       <c r="Z26" t="inlineStr"/>
-      <c r="AA26" t="inlineStr"/>
-      <c r="AB26" t="inlineStr"/>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>1630969</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>2020-06-10</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>HT-AF-HEALTH-188378-GO-DIR</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>1630969</t>
-        </is>
-      </c>
-      <c r="AL26" t="inlineStr">
-        <is>
-          <t>2020-06-10</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>HT-AF-HEALTH-188378-GO-DIR</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
           <t>Haiti COVID-19 Response</t>
         </is>
       </c>
-      <c r="AO26" t="inlineStr">
+      <c r="AG26" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1630969</t>
         </is>
@@ -4401,49 +4061,37 @@
       </c>
       <c r="Y27" t="inlineStr"/>
       <c r="Z27" t="inlineStr"/>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1607231</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>2020-06-09</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>B-3-6-A-Lote2</t>
+        </is>
+      </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>1607231</t>
-        </is>
-      </c>
-      <c r="AL27" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>B-3-6-A-Lote2</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
           <t>Distribution Grid Modernization and Loss Reduction Project</t>
         </is>
       </c>
-      <c r="AO27" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607231</t>
         </is>
@@ -4548,49 +4196,37 @@
       </c>
       <c r="Y28" t="inlineStr"/>
       <c r="Z28" t="inlineStr"/>
-      <c r="AA28" t="inlineStr"/>
-      <c r="AB28" t="inlineStr"/>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>1607230</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>2020-06-09</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>B-3-6-A-Lote1</t>
+        </is>
+      </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>1607230</t>
-        </is>
-      </c>
-      <c r="AL28" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>B-3-6-A-Lote1</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
           <t>Distribution Grid Modernization and Loss Reduction Project</t>
         </is>
       </c>
-      <c r="AO28" t="inlineStr">
+      <c r="AG28" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607230</t>
         </is>
@@ -4695,49 +4331,37 @@
       </c>
       <c r="Y29" t="inlineStr"/>
       <c r="Z29" t="inlineStr"/>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>1607216</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>2020-06-09</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>B-3-6-A-Lote3</t>
+        </is>
+      </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>1607216</t>
-        </is>
-      </c>
-      <c r="AL29" t="inlineStr">
-        <is>
-          <t>2020-06-09</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>B-3-6-A-Lote3</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
           <t>Distribution Grid Modernization and Loss Reduction Project</t>
         </is>
       </c>
-      <c r="AO29" t="inlineStr">
+      <c r="AG29" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1607216</t>
         </is>
@@ -4842,49 +4466,37 @@
       </c>
       <c r="Y30" t="inlineStr"/>
       <c r="Z30" t="inlineStr"/>
-      <c r="AA30" t="inlineStr"/>
-      <c r="AB30" t="inlineStr"/>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1620679</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>2020-04-16</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>GO-DIR-06-2020</t>
+        </is>
+      </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>1620679</t>
-        </is>
-      </c>
-      <c r="AL30" t="inlineStr">
-        <is>
-          <t>2020-04-16</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>GO-DIR-06-2020</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
           <t>AR: COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO30" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1620679</t>
         </is>
@@ -4989,49 +4601,37 @@
       </c>
       <c r="Y31" t="inlineStr"/>
       <c r="Z31" t="inlineStr"/>
-      <c r="AA31" t="inlineStr"/>
-      <c r="AB31" t="inlineStr"/>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>1615872</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>2020-04-13</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>GO-DIR-05-2020</t>
+        </is>
+      </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>1615872</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>2020-04-13</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>GO-DIR-05-2020</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
           <t>AR: COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO31" t="inlineStr">
+      <c r="AG31" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615872</t>
         </is>
@@ -5136,49 +4736,37 @@
       </c>
       <c r="Y32" t="inlineStr"/>
       <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>1615865</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>2020-04-13</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>GO-DIR-04-2020</t>
+        </is>
+      </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>1615865</t>
-        </is>
-      </c>
-      <c r="AL32" t="inlineStr">
-        <is>
-          <t>2020-04-13</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>GO-DIR-04-2020</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
           <t>AR: COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO32" t="inlineStr">
+      <c r="AG32" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615865</t>
         </is>
@@ -5283,49 +4871,37 @@
       </c>
       <c r="Y33" t="inlineStr"/>
       <c r="Z33" t="inlineStr"/>
-      <c r="AA33" t="inlineStr"/>
-      <c r="AB33" t="inlineStr"/>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>1615710</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>2020-04-13</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>GO-DIR-03-2020</t>
+        </is>
+      </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>Direct Selection</t>
-        </is>
-      </c>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>1615710</t>
-        </is>
-      </c>
-      <c r="AL33" t="inlineStr">
-        <is>
-          <t>2020-04-13</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>GO-DIR-03-2020</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
           <t>AR: COVID-19 Emergency Response Project</t>
         </is>
       </c>
-      <c r="AO33" t="inlineStr">
+      <c r="AG33" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1615710</t>
         </is>
@@ -5430,49 +5006,37 @@
       </c>
       <c r="Y34" t="inlineStr"/>
       <c r="Z34" t="inlineStr"/>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>1606341</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>2019-12-09</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>AR-MSAL-71694-GO-RFB Lote 1</t>
+        </is>
+      </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>1606341</t>
-        </is>
-      </c>
-      <c r="AL34" t="inlineStr">
-        <is>
-          <t>2019-12-09</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>AR-MSAL-71694-GO-RFB Lote 1</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
           <t>Provincial Public Health Insurance Development Project</t>
         </is>
       </c>
-      <c r="AO34" t="inlineStr">
+      <c r="AG34" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1606341</t>
         </is>
@@ -5577,49 +5141,37 @@
       </c>
       <c r="Y35" t="inlineStr"/>
       <c r="Z35" t="inlineStr"/>
-      <c r="AA35" t="inlineStr"/>
-      <c r="AB35" t="inlineStr"/>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>1616717</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>2019-09-27</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>PE-PROVIAS-163546-CW-RFB</t>
+        </is>
+      </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>1616717</t>
-        </is>
-      </c>
-      <c r="AL35" t="inlineStr">
-        <is>
-          <t>2019-09-27</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>PE-PROVIAS-163546-CW-RFB</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
           <t>Support to the Subnational Transport Program Project</t>
         </is>
       </c>
-      <c r="AO35" t="inlineStr">
+      <c r="AG35" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1616717</t>
         </is>
@@ -5724,49 +5276,37 @@
       </c>
       <c r="Y36" t="inlineStr"/>
       <c r="Z36" t="inlineStr"/>
-      <c r="AA36" t="inlineStr"/>
-      <c r="AB36" t="inlineStr"/>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>1580217</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>2018-12-10</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>AR-PHIP-640-B-LPI</t>
+        </is>
+      </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>1580217</t>
-        </is>
-      </c>
-      <c r="AL36" t="inlineStr">
-        <is>
-          <t>2018-12-10</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>AR-PHIP-640-B-LPI</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
           <t>Provincial Public Health Insurance Development Project</t>
         </is>
       </c>
-      <c r="AO36" t="inlineStr">
+      <c r="AG36" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1580217</t>
         </is>
@@ -5871,49 +5411,37 @@
       </c>
       <c r="Y37" t="inlineStr"/>
       <c r="Z37" t="inlineStr"/>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>1562978</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>2018-09-11</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>ABC Nro 711/18 GNT-SCT-MRH-BM</t>
+        </is>
+      </c>
       <c r="AF37" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>1562978</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>2018-09-11</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>ABC Nro 711/18 GNT-SCT-MRH-BM</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
           <t>Santa Cruz Road Corridor Connector Project (San Ignacio - San Jose)</t>
         </is>
       </c>
-      <c r="AO37" t="inlineStr">
+      <c r="AG37" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1562978</t>
         </is>
@@ -6018,49 +5546,37 @@
       </c>
       <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr"/>
-      <c r="AA38" t="inlineStr"/>
-      <c r="AB38" t="inlineStr"/>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1562888</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>2018-07-05</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>8634 - AR-MINCYT-28511-GO-RFB</t>
+        </is>
+      </c>
       <c r="AF38" t="inlineStr">
         <is>
-          <t>Request for Proposals</t>
-        </is>
-      </c>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>1562888</t>
-        </is>
-      </c>
-      <c r="AL38" t="inlineStr">
-        <is>
-          <t>2018-07-05</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>8634 - AR-MINCYT-28511-GO-RFB</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
           <t>Unleashing Productive Innovation Project</t>
         </is>
       </c>
-      <c r="AO38" t="inlineStr">
+      <c r="AG38" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1562888</t>
         </is>
@@ -6161,49 +5677,37 @@
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="inlineStr"/>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>1566879</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>2018-05-28</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>3B23 -CS-SNPDH</t>
+        </is>
+      </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>Individual Consultant Selection</t>
-        </is>
-      </c>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>1566879</t>
-        </is>
-      </c>
-      <c r="AL39" t="inlineStr">
-        <is>
-          <t>2018-05-28</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>3B23 -CS-SNPDH</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
           <t>Second Bolsa Família</t>
         </is>
       </c>
-      <c r="AO39" t="inlineStr">
+      <c r="AG39" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1566879</t>
         </is>
@@ -6308,49 +5812,37 @@
       </c>
       <c r="Y40" t="inlineStr"/>
       <c r="Z40" t="inlineStr"/>
-      <c r="AA40" t="inlineStr"/>
-      <c r="AB40" t="inlineStr"/>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>1560811</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>ABC No 495/18 GNT-SCV-MRH-BM</t>
+        </is>
+      </c>
       <c r="AF40" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>1560811</t>
-        </is>
-      </c>
-      <c r="AL40" t="inlineStr">
-        <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>ABC No 495/18 GNT-SCV-MRH-BM</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
           <t>BO Road Sector Capacity Development Project</t>
         </is>
       </c>
-      <c r="AO40" t="inlineStr">
+      <c r="AG40" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1560811</t>
         </is>
@@ -6455,49 +5947,37 @@
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="inlineStr"/>
-      <c r="AA41" t="inlineStr"/>
-      <c r="AB41" t="inlineStr"/>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1560809</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>2018-05-17</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>ABC No 494/18 GNT-SCV-MRJ-BM</t>
+        </is>
+      </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>1560809</t>
-        </is>
-      </c>
-      <c r="AL41" t="inlineStr">
-        <is>
-          <t>2018-05-17</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>ABC No 494/18 GNT-SCV-MRJ-BM</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
           <t>BO Road Sector Capacity Development Project</t>
         </is>
       </c>
-      <c r="AO41" t="inlineStr">
+      <c r="AG41" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1560809</t>
         </is>
@@ -6602,49 +6082,37 @@
       </c>
       <c r="Y42" t="inlineStr"/>
       <c r="Z42" t="inlineStr"/>
-      <c r="AA42" t="inlineStr"/>
-      <c r="AB42" t="inlineStr"/>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>1554457</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>2018-04-12</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>BIRF-8542-LPI-B-2016-001</t>
+        </is>
+      </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>1554457</t>
-        </is>
-      </c>
-      <c r="AL42" t="inlineStr">
-        <is>
-          <t>2018-04-12</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>BIRF-8542-LPI-B-2016-001</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
           <t>Supporting Education Reform in Targeted Circuits</t>
         </is>
       </c>
-      <c r="AO42" t="inlineStr">
+      <c r="AG42" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1554457</t>
         </is>
@@ -6745,49 +6213,37 @@
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="inlineStr"/>
-      <c r="AA43" t="inlineStr"/>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>1543474</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>2017-02-03</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>FSSPSV-281-LPI-B</t>
+        </is>
+      </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>1543474</t>
-        </is>
-      </c>
-      <c r="AL43" t="inlineStr">
-        <is>
-          <t>2017-02-03</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>FSSPSV-281-LPI-B</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
           <t>STRENGTHENING PUBLIC HEALTH CARE SYSTEM</t>
         </is>
       </c>
-      <c r="AO43" t="inlineStr">
+      <c r="AG43" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1543474</t>
         </is>
@@ -6888,49 +6344,37 @@
       </c>
       <c r="Y44" t="inlineStr"/>
       <c r="Z44" t="inlineStr"/>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>1543384</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>2016-11-21</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>No. FSSPSV-277-LPI-B</t>
+        </is>
+      </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>1543384</t>
-        </is>
-      </c>
-      <c r="AL44" t="inlineStr">
-        <is>
-          <t>2016-11-21</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>No. FSSPSV-277-LPI-B</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
           <t>STRENGTHENING PUBLIC HEALTH CARE SYSTEM</t>
         </is>
       </c>
-      <c r="AO44" t="inlineStr">
+      <c r="AG44" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1543384</t>
         </is>
@@ -7031,45 +6475,33 @@
       </c>
       <c r="Y45" t="inlineStr"/>
       <c r="Z45" t="inlineStr"/>
-      <c r="AA45" t="inlineStr"/>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB45" t="inlineStr"/>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1542734</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>2016-08-17</t>
+        </is>
+      </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>1542734</t>
-        </is>
-      </c>
-      <c r="AL45" t="inlineStr">
-        <is>
-          <t>2016-08-17</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
           <t>6560/2016</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
+      <c r="AF45" t="inlineStr">
         <is>
           <t>PY Energy Sector Strengthening Project</t>
         </is>
       </c>
-      <c r="AO45" t="inlineStr">
+      <c r="AG45" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1542734</t>
         </is>
@@ -7174,49 +6606,37 @@
       </c>
       <c r="Y46" t="inlineStr"/>
       <c r="Z46" t="inlineStr"/>
-      <c r="AA46" t="inlineStr"/>
-      <c r="AB46" t="inlineStr"/>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>1535131</t>
+        </is>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>2015-11-09</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>PHIP-3-LPI-B-8</t>
+        </is>
+      </c>
       <c r="AF46" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>1535131</t>
-        </is>
-      </c>
-      <c r="AL46" t="inlineStr">
-        <is>
-          <t>2015-11-09</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>PHIP-3-LPI-B-8</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
           <t>Provincial Public Health Insurance Development Project</t>
         </is>
       </c>
-      <c r="AO46" t="inlineStr">
+      <c r="AG46" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1535131</t>
         </is>
@@ -7321,49 +6741,37 @@
       </c>
       <c r="Y47" t="inlineStr"/>
       <c r="Z47" t="inlineStr"/>
-      <c r="AA47" t="inlineStr"/>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>1541158</t>
+        </is>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>2015-08-05</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>DVRP/NCBW/01</t>
+        </is>
+      </c>
       <c r="AF47" t="inlineStr">
         <is>
-          <t>National Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>1541158</t>
-        </is>
-      </c>
-      <c r="AL47" t="inlineStr">
-        <is>
-          <t>2015-08-05</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>DVRP/NCBW/01</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
           <t>Regional Disaster Vulnerability Reduction APL1 - Grenada and St. Vincent and the Grenadines</t>
         </is>
       </c>
-      <c r="AO47" t="inlineStr">
+      <c r="AG47" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1541158</t>
         </is>
@@ -7464,49 +6872,37 @@
       </c>
       <c r="Y48" t="inlineStr"/>
       <c r="Z48" t="inlineStr"/>
-      <c r="AA48" t="inlineStr"/>
-      <c r="AB48" t="inlineStr"/>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1530142</t>
+        </is>
+      </c>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>2015-04-14</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>764/2014</t>
+        </is>
+      </c>
       <c r="AF48" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>1530142</t>
-        </is>
-      </c>
-      <c r="AL48" t="inlineStr">
-        <is>
-          <t>2015-04-14</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>764/2014</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
           <t>PY Energy Sector Strengthening Project</t>
         </is>
       </c>
-      <c r="AO48" t="inlineStr">
+      <c r="AG48" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1530142</t>
         </is>
@@ -7607,49 +7003,37 @@
       </c>
       <c r="Y49" t="inlineStr"/>
       <c r="Z49" t="inlineStr"/>
-      <c r="AA49" t="inlineStr"/>
-      <c r="AB49" t="inlineStr"/>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1527391</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>2015-02-17</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>ANDE-BIRF N 756/2014</t>
+        </is>
+      </c>
       <c r="AF49" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>1527391</t>
-        </is>
-      </c>
-      <c r="AL49" t="inlineStr">
-        <is>
-          <t>2015-02-17</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>ANDE-BIRF N 756/2014</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
           <t>PY Energy Sector Strengthening Project</t>
         </is>
       </c>
-      <c r="AO49" t="inlineStr">
+      <c r="AG49" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527391</t>
         </is>
@@ -7750,49 +7134,37 @@
       </c>
       <c r="Y50" t="inlineStr"/>
       <c r="Z50" t="inlineStr"/>
-      <c r="AA50" t="inlineStr"/>
-      <c r="AB50" t="inlineStr"/>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1527390</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>2015-02-17</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>ANDE-BIRF N 756/2014</t>
+        </is>
+      </c>
       <c r="AF50" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>1527390</t>
-        </is>
-      </c>
-      <c r="AL50" t="inlineStr">
-        <is>
-          <t>2015-02-17</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>ANDE-BIRF N 756/2014</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
           <t>PY Energy Sector Strengthening Project</t>
         </is>
       </c>
-      <c r="AO50" t="inlineStr">
+      <c r="AG50" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527390</t>
         </is>
@@ -7893,49 +7265,37 @@
       </c>
       <c r="Y51" t="inlineStr"/>
       <c r="Z51" t="inlineStr"/>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>1527389</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>2015-02-17</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>ANDE-BIRF N 756/2014</t>
+        </is>
+      </c>
       <c r="AF51" t="inlineStr">
         <is>
-          <t>Request for Bids</t>
-        </is>
-      </c>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>1527389</t>
-        </is>
-      </c>
-      <c r="AL51" t="inlineStr">
-        <is>
-          <t>2015-02-17</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>ANDE-BIRF N 756/2014</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
           <t>PY Energy Sector Strengthening Project</t>
         </is>
       </c>
-      <c r="AO51" t="inlineStr">
+      <c r="AG51" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1527389</t>
         </is>
@@ -8040,49 +7400,37 @@
       </c>
       <c r="Y52" t="inlineStr"/>
       <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>1507024</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>2013-03-28</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>LPI 02/05/2011-Adquisicion Equip Basico</t>
+        </is>
+      </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>Limited International Bidding</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>1507024</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>2013-03-28</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>LPI 02/05/2011-Adquisicion Equip Basico</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
           <t>Improving Community and Family Health Care Services Project</t>
         </is>
       </c>
-      <c r="AO52" t="inlineStr">
+      <c r="AG52" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1507024</t>
         </is>
@@ -8183,49 +7531,37 @@
       </c>
       <c r="Y53" t="inlineStr"/>
       <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>1327057</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>2012-10-24</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>No. 018/ASJUR/12</t>
+        </is>
+      </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>1327057</t>
-        </is>
-      </c>
-      <c r="AL53" t="inlineStr">
-        <is>
-          <t>2012-10-24</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>No. 018/ASJUR/12</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
           <t>Upgrading and Greening the Rio de Janeiro Urban Rail System</t>
         </is>
       </c>
-      <c r="AO53" t="inlineStr">
+      <c r="AG53" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1327057</t>
         </is>
@@ -8330,49 +7666,37 @@
       </c>
       <c r="Y54" t="inlineStr"/>
       <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1325071</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>2012-08-28</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>FESP-292-B</t>
+        </is>
+      </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>1325071</t>
-        </is>
-      </c>
-      <c r="AL54" t="inlineStr">
-        <is>
-          <t>2012-08-28</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>FESP-292-B</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
           <t>AR- Essential Public Health Functions</t>
         </is>
       </c>
-      <c r="AO54" t="inlineStr">
+      <c r="AG54" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1325071</t>
         </is>
@@ -8473,49 +7797,37 @@
       </c>
       <c r="Y55" t="inlineStr"/>
       <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>1284880</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>2009-06-23</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>006/asjur/09</t>
+        </is>
+      </c>
       <c r="AF55" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>1284880</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>2009-06-23</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>006/asjur/09</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
           <t>Upgrading and Greening the Rio de Janeiro Urban Rail System</t>
         </is>
       </c>
-      <c r="AO55" t="inlineStr">
+      <c r="AG55" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1284880</t>
         </is>
@@ -8620,49 +7932,37 @@
       </c>
       <c r="Y56" t="inlineStr"/>
       <c r="Z56" t="inlineStr"/>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>1255975</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>2005-11-29</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>SL/WB-ICB-W-01/05(B) ANSE LA RAYE</t>
+        </is>
+      </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>1255975</t>
-        </is>
-      </c>
-      <c r="AL56" t="inlineStr">
-        <is>
-          <t>2005-11-29</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>SL/WB-ICB-W-01/05(B) ANSE LA RAYE</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
           <t>ST. LUCIA Education Development Project</t>
         </is>
       </c>
-      <c r="AO56" t="inlineStr">
+      <c r="AG56" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1255975</t>
         </is>
@@ -8767,49 +8067,37 @@
       </c>
       <c r="Y57" t="inlineStr"/>
       <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>1256115</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>2005-10-29</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>SL/WB-ICB-W-01/05(A) GROS ISLET</t>
+        </is>
+      </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>1256115</t>
-        </is>
-      </c>
-      <c r="AL57" t="inlineStr">
-        <is>
-          <t>2005-10-29</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>SL/WB-ICB-W-01/05(A) GROS ISLET</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
           <t>ST. LUCIA Education Development Project</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
+      <c r="AG57" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1256115</t>
         </is>
@@ -8910,49 +8198,37 @@
       </c>
       <c r="Y58" t="inlineStr"/>
       <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>1240081</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>2004-04-02</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>FF31A HOLLEY GROPU CO. LTD.</t>
+        </is>
+      </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>1240081</t>
-        </is>
-      </c>
-      <c r="AL58" t="inlineStr">
-        <is>
-          <t>2004-04-02</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>FF31A HOLLEY GROPU CO. LTD.</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
           <t>Uruguay Power Transmission &amp; Distribution Project</t>
         </is>
       </c>
-      <c r="AO58" t="inlineStr">
+      <c r="AG58" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1240081</t>
         </is>
@@ -9057,49 +8333,37 @@
       </c>
       <c r="Y59" t="inlineStr"/>
       <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>1224257</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>2002-08-06</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>ARGON S.R.L. - 106/2.002N (LPI 01-2001)</t>
+        </is>
+      </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>1224257</t>
-        </is>
-      </c>
-      <c r="AL59" t="inlineStr">
-        <is>
-          <t>2002-08-06</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>ARGON S.R.L. - 106/2.002N (LPI 01-2001)</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
           <t>PY-Maternal Health and Child Development Project</t>
         </is>
       </c>
-      <c r="AO59" t="inlineStr">
+      <c r="AG59" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1224257</t>
         </is>
@@ -9200,49 +8464,37 @@
       </c>
       <c r="Y60" t="inlineStr"/>
       <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>1215237</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>2002-04-12</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>FF31, HOLLEY GROUP CO. LTD. (ITEM 2)</t>
+        </is>
+      </c>
       <c r="AF60" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>1215237</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>2002-04-12</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>FF31, HOLLEY GROUP CO. LTD. (ITEM 2)</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
           <t>Uruguay Power Transmission &amp; Distribution Project</t>
         </is>
       </c>
-      <c r="AO60" t="inlineStr">
+      <c r="AG60" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1215237</t>
         </is>
@@ -9347,49 +8599,37 @@
       </c>
       <c r="Y61" t="inlineStr"/>
       <c r="Z61" t="inlineStr"/>
-      <c r="AA61" t="inlineStr"/>
-      <c r="AB61" t="inlineStr"/>
-      <c r="AC61" t="inlineStr"/>
-      <c r="AD61" t="inlineStr"/>
-      <c r="AE61" t="inlineStr"/>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>1211670</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>2001-06-27</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>ARGON LOTE 4,5,;9,4; 12.2;15.3</t>
+        </is>
+      </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>International Competitive Bidding</t>
-        </is>
-      </c>
-      <c r="AG61" t="inlineStr"/>
-      <c r="AH61" t="inlineStr"/>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>1211670</t>
-        </is>
-      </c>
-      <c r="AL61" t="inlineStr">
-        <is>
-          <t>2001-06-27</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>ARGON LOTE 4,5,;9,4; 12.2;15.3</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
           <t>PY-Maternal Health and Child Development Project</t>
         </is>
       </c>
-      <c r="AO61" t="inlineStr">
+      <c r="AG61" t="inlineStr">
         <is>
           <t>https://projects.worldbank.org/en/projects-operations/contractoverview/1211670</t>
         </is>
@@ -9494,29 +8734,21 @@
       </c>
       <c r="Y62" t="inlineStr"/>
       <c r="Z62" t="inlineStr"/>
-      <c r="AA62" t="inlineStr"/>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB62" t="inlineStr"/>
       <c r="AC62" t="inlineStr"/>
       <c r="AD62" t="inlineStr"/>
       <c r="AE62" t="inlineStr"/>
-      <c r="AF62" t="inlineStr"/>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>Health Services Improvement Project</t>
+        </is>
+      </c>
       <c r="AG62" t="inlineStr"/>
-      <c r="AH62" t="inlineStr"/>
-      <c r="AI62" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr"/>
-      <c r="AK62" t="inlineStr"/>
-      <c r="AL62" t="inlineStr"/>
-      <c r="AM62" t="inlineStr"/>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>Health Services Improvement Project</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -9617,29 +8849,21 @@
       </c>
       <c r="Y63" t="inlineStr"/>
       <c r="Z63" t="inlineStr"/>
-      <c r="AA63" t="inlineStr"/>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB63" t="inlineStr"/>
       <c r="AC63" t="inlineStr"/>
       <c r="AD63" t="inlineStr"/>
       <c r="AE63" t="inlineStr"/>
-      <c r="AF63" t="inlineStr"/>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>Health Services Support Program</t>
+        </is>
+      </c>
       <c r="AG63" t="inlineStr"/>
-      <c r="AH63" t="inlineStr"/>
-      <c r="AI63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr"/>
-      <c r="AK63" t="inlineStr"/>
-      <c r="AL63" t="inlineStr"/>
-      <c r="AM63" t="inlineStr"/>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>Health Services Support Program</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -9740,29 +8964,21 @@
       </c>
       <c r="Y64" t="inlineStr"/>
       <c r="Z64" t="inlineStr"/>
-      <c r="AA64" t="inlineStr"/>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB64" t="inlineStr"/>
       <c r="AC64" t="inlineStr"/>
       <c r="AD64" t="inlineStr"/>
       <c r="AE64" t="inlineStr"/>
-      <c r="AF64" t="inlineStr"/>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>Electricity Infrastructure Expansion Program</t>
+        </is>
+      </c>
       <c r="AG64" t="inlineStr"/>
-      <c r="AH64" t="inlineStr"/>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr"/>
-      <c r="AK64" t="inlineStr"/>
-      <c r="AL64" t="inlineStr"/>
-      <c r="AM64" t="inlineStr"/>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>Electricity Infrastructure Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -9863,29 +9079,21 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="inlineStr"/>
-      <c r="AA65" t="inlineStr"/>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB65" t="inlineStr"/>
       <c r="AC65" t="inlineStr"/>
       <c r="AD65" t="inlineStr"/>
       <c r="AE65" t="inlineStr"/>
-      <c r="AF65" t="inlineStr"/>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>Consolidating a Sustainable Energy Sector</t>
+        </is>
+      </c>
       <c r="AG65" t="inlineStr"/>
-      <c r="AH65" t="inlineStr"/>
-      <c r="AI65" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr"/>
-      <c r="AK65" t="inlineStr"/>
-      <c r="AL65" t="inlineStr"/>
-      <c r="AM65" t="inlineStr"/>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>Consolidating a Sustainable Energy Sector</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -9986,29 +9194,21 @@
       </c>
       <c r="Y66" t="inlineStr"/>
       <c r="Z66" t="inlineStr"/>
-      <c r="AA66" t="inlineStr"/>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB66" t="inlineStr"/>
       <c r="AC66" t="inlineStr"/>
       <c r="AD66" t="inlineStr"/>
       <c r="AE66" t="inlineStr"/>
-      <c r="AF66" t="inlineStr"/>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>Electricity Infrastructure Expansion Program</t>
+        </is>
+      </c>
       <c r="AG66" t="inlineStr"/>
-      <c r="AH66" t="inlineStr"/>
-      <c r="AI66" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr"/>
-      <c r="AK66" t="inlineStr"/>
-      <c r="AL66" t="inlineStr"/>
-      <c r="AM66" t="inlineStr"/>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>Electricity Infrastructure Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -10109,29 +9309,21 @@
       </c>
       <c r="Y67" t="inlineStr"/>
       <c r="Z67" t="inlineStr"/>
-      <c r="AA67" t="inlineStr"/>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB67" t="inlineStr"/>
       <c r="AC67" t="inlineStr"/>
       <c r="AD67" t="inlineStr"/>
       <c r="AE67" t="inlineStr"/>
-      <c r="AF67" t="inlineStr"/>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>Consolidating a Sustainable Energy Sector</t>
+        </is>
+      </c>
       <c r="AG67" t="inlineStr"/>
-      <c r="AH67" t="inlineStr"/>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr"/>
-      <c r="AK67" t="inlineStr"/>
-      <c r="AL67" t="inlineStr"/>
-      <c r="AM67" t="inlineStr"/>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>Consolidating a Sustainable Energy Sector</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -10232,29 +9424,21 @@
       </c>
       <c r="Y68" t="inlineStr"/>
       <c r="Z68" t="inlineStr"/>
-      <c r="AA68" t="inlineStr"/>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB68" t="inlineStr"/>
       <c r="AC68" t="inlineStr"/>
       <c r="AD68" t="inlineStr"/>
       <c r="AE68" t="inlineStr"/>
-      <c r="AF68" t="inlineStr"/>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>Electricity Infrastructure Expansion Program</t>
+        </is>
+      </c>
       <c r="AG68" t="inlineStr"/>
-      <c r="AH68" t="inlineStr"/>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr"/>
-      <c r="AK68" t="inlineStr"/>
-      <c r="AL68" t="inlineStr"/>
-      <c r="AM68" t="inlineStr"/>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>Electricity Infrastructure Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -10355,29 +9539,21 @@
       </c>
       <c r="Y69" t="inlineStr"/>
       <c r="Z69" t="inlineStr"/>
-      <c r="AA69" t="inlineStr"/>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB69" t="inlineStr"/>
       <c r="AC69" t="inlineStr"/>
       <c r="AD69" t="inlineStr"/>
       <c r="AE69" t="inlineStr"/>
-      <c r="AF69" t="inlineStr"/>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>Comprehensive urban urban development program with tourist vocations</t>
+        </is>
+      </c>
       <c r="AG69" t="inlineStr"/>
-      <c r="AH69" t="inlineStr"/>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr"/>
-      <c r="AK69" t="inlineStr"/>
-      <c r="AL69" t="inlineStr"/>
-      <c r="AM69" t="inlineStr"/>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>Comprehensive urban urban development program with tourist vocations</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -10478,29 +9654,21 @@
       </c>
       <c r="Y70" t="inlineStr"/>
       <c r="Z70" t="inlineStr"/>
-      <c r="AA70" t="inlineStr"/>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr"/>
       <c r="AD70" t="inlineStr"/>
       <c r="AE70" t="inlineStr"/>
-      <c r="AF70" t="inlineStr"/>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>Consolidating a Sustainable Energy Sector</t>
+        </is>
+      </c>
       <c r="AG70" t="inlineStr"/>
-      <c r="AH70" t="inlineStr"/>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr"/>
-      <c r="AK70" t="inlineStr"/>
-      <c r="AL70" t="inlineStr"/>
-      <c r="AM70" t="inlineStr"/>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>Consolidating a Sustainable Energy Sector</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -10601,29 +9769,21 @@
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="inlineStr"/>
-      <c r="AA71" t="inlineStr"/>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB71" t="inlineStr"/>
       <c r="AC71" t="inlineStr"/>
       <c r="AD71" t="inlineStr"/>
       <c r="AE71" t="inlineStr"/>
-      <c r="AF71" t="inlineStr"/>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>Deployment of Cleaner Fuels and Renewable Energies in Barbados</t>
+        </is>
+      </c>
       <c r="AG71" t="inlineStr"/>
-      <c r="AH71" t="inlineStr"/>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr"/>
-      <c r="AK71" t="inlineStr"/>
-      <c r="AL71" t="inlineStr"/>
-      <c r="AM71" t="inlineStr"/>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>Deployment of Cleaner Fuels and Renewable Energies in Barbados</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -10724,29 +9884,21 @@
       </c>
       <c r="Y72" t="inlineStr"/>
       <c r="Z72" t="inlineStr"/>
-      <c r="AA72" t="inlineStr"/>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB72" t="inlineStr"/>
       <c r="AC72" t="inlineStr"/>
       <c r="AD72" t="inlineStr"/>
       <c r="AE72" t="inlineStr"/>
-      <c r="AF72" t="inlineStr"/>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>Consolidating a Sustainable Energy Sector</t>
+        </is>
+      </c>
       <c r="AG72" t="inlineStr"/>
-      <c r="AH72" t="inlineStr"/>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr"/>
-      <c r="AK72" t="inlineStr"/>
-      <c r="AL72" t="inlineStr"/>
-      <c r="AM72" t="inlineStr"/>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>Consolidating a Sustainable Energy Sector</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -10847,29 +9999,21 @@
       </c>
       <c r="Y73" t="inlineStr"/>
       <c r="Z73" t="inlineStr"/>
-      <c r="AA73" t="inlineStr"/>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB73" t="inlineStr"/>
       <c r="AC73" t="inlineStr"/>
       <c r="AD73" t="inlineStr"/>
       <c r="AE73" t="inlineStr"/>
-      <c r="AF73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>Paramaribo Urban Rehabilitation Program</t>
+        </is>
+      </c>
       <c r="AG73" t="inlineStr"/>
-      <c r="AH73" t="inlineStr"/>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr"/>
-      <c r="AK73" t="inlineStr"/>
-      <c r="AL73" t="inlineStr"/>
-      <c r="AM73" t="inlineStr"/>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>Paramaribo Urban Rehabilitation Program</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -10970,29 +10114,21 @@
       </c>
       <c r="Y74" t="inlineStr"/>
       <c r="Z74" t="inlineStr"/>
-      <c r="AA74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB74" t="inlineStr"/>
       <c r="AC74" t="inlineStr"/>
       <c r="AD74" t="inlineStr"/>
       <c r="AE74" t="inlineStr"/>
-      <c r="AF74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr">
+        <is>
+          <t>Trinidad and Tobago National Water Sector Transformation Program</t>
+        </is>
+      </c>
       <c r="AG74" t="inlineStr"/>
-      <c r="AH74" t="inlineStr"/>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr"/>
-      <c r="AK74" t="inlineStr"/>
-      <c r="AL74" t="inlineStr"/>
-      <c r="AM74" t="inlineStr"/>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>Trinidad and Tobago National Water Sector Transformation Program</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -11093,29 +10229,21 @@
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="inlineStr"/>
-      <c r="AA75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB75" t="inlineStr"/>
       <c r="AC75" t="inlineStr"/>
       <c r="AD75" t="inlineStr"/>
       <c r="AE75" t="inlineStr"/>
-      <c r="AF75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr">
+        <is>
+          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
+        </is>
+      </c>
       <c r="AG75" t="inlineStr"/>
-      <c r="AH75" t="inlineStr"/>
-      <c r="AI75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr"/>
-      <c r="AK75" t="inlineStr"/>
-      <c r="AL75" t="inlineStr"/>
-      <c r="AM75" t="inlineStr"/>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -11216,29 +10344,21 @@
       </c>
       <c r="Y76" t="inlineStr"/>
       <c r="Z76" t="inlineStr"/>
-      <c r="AA76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB76" t="inlineStr"/>
       <c r="AC76" t="inlineStr"/>
       <c r="AD76" t="inlineStr"/>
       <c r="AE76" t="inlineStr"/>
-      <c r="AF76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr">
+        <is>
+          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
+        </is>
+      </c>
       <c r="AG76" t="inlineStr"/>
-      <c r="AH76" t="inlineStr"/>
-      <c r="AI76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr"/>
-      <c r="AK76" t="inlineStr"/>
-      <c r="AL76" t="inlineStr"/>
-      <c r="AM76" t="inlineStr"/>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -11339,29 +10459,21 @@
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="inlineStr"/>
-      <c r="AA77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB77" t="inlineStr"/>
       <c r="AC77" t="inlineStr"/>
       <c r="AD77" t="inlineStr"/>
       <c r="AE77" t="inlineStr"/>
-      <c r="AF77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>Electricity Infrastructure Expansion Program</t>
+        </is>
+      </c>
       <c r="AG77" t="inlineStr"/>
-      <c r="AH77" t="inlineStr"/>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr"/>
-      <c r="AK77" t="inlineStr"/>
-      <c r="AL77" t="inlineStr"/>
-      <c r="AM77" t="inlineStr"/>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>Electricity Infrastructure Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -11462,29 +10574,21 @@
       </c>
       <c r="Y78" t="inlineStr"/>
       <c r="Z78" t="inlineStr"/>
-      <c r="AA78" t="inlineStr"/>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB78" t="inlineStr"/>
       <c r="AC78" t="inlineStr"/>
       <c r="AD78" t="inlineStr"/>
       <c r="AE78" t="inlineStr"/>
-      <c r="AF78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr">
+        <is>
+          <t>Sustainable Agricultural Productivity Program</t>
+        </is>
+      </c>
       <c r="AG78" t="inlineStr"/>
-      <c r="AH78" t="inlineStr"/>
-      <c r="AI78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr"/>
-      <c r="AK78" t="inlineStr"/>
-      <c r="AL78" t="inlineStr"/>
-      <c r="AM78" t="inlineStr"/>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>Sustainable Agricultural Productivity Program</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -11585,29 +10689,21 @@
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="inlineStr"/>
-      <c r="AA79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB79" t="inlineStr"/>
       <c r="AC79" t="inlineStr"/>
       <c r="AD79" t="inlineStr"/>
       <c r="AE79" t="inlineStr"/>
-      <c r="AF79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr">
+        <is>
+          <t>Improving Tax and Customs Revenue Collection Services Through Digital Transformation</t>
+        </is>
+      </c>
       <c r="AG79" t="inlineStr"/>
-      <c r="AH79" t="inlineStr"/>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr"/>
-      <c r="AK79" t="inlineStr"/>
-      <c r="AL79" t="inlineStr"/>
-      <c r="AM79" t="inlineStr"/>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>Improving Tax and Customs Revenue Collection Services Through Digital Transformation</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -11708,29 +10804,21 @@
       </c>
       <c r="Y80" t="inlineStr"/>
       <c r="Z80" t="inlineStr"/>
-      <c r="AA80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB80" t="inlineStr"/>
       <c r="AC80" t="inlineStr"/>
       <c r="AD80" t="inlineStr"/>
       <c r="AE80" t="inlineStr"/>
-      <c r="AF80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr">
+        <is>
+          <t>Electricity Infrastructure Expansion Program</t>
+        </is>
+      </c>
       <c r="AG80" t="inlineStr"/>
-      <c r="AH80" t="inlineStr"/>
-      <c r="AI80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr"/>
-      <c r="AK80" t="inlineStr"/>
-      <c r="AL80" t="inlineStr"/>
-      <c r="AM80" t="inlineStr"/>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>Electricity Infrastructure Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -11827,29 +10915,21 @@
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="inlineStr"/>
-      <c r="AA81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB81" t="inlineStr"/>
       <c r="AC81" t="inlineStr"/>
       <c r="AD81" t="inlineStr"/>
       <c r="AE81" t="inlineStr"/>
-      <c r="AF81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr">
+        <is>
+          <t>Health Services Improvement Project</t>
+        </is>
+      </c>
       <c r="AG81" t="inlineStr"/>
-      <c r="AH81" t="inlineStr"/>
-      <c r="AI81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr"/>
-      <c r="AK81" t="inlineStr"/>
-      <c r="AL81" t="inlineStr"/>
-      <c r="AM81" t="inlineStr"/>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>Health Services Improvement Project</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -11950,29 +11030,21 @@
       </c>
       <c r="Y82" t="inlineStr"/>
       <c r="Z82" t="inlineStr"/>
-      <c r="AA82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB82" t="inlineStr"/>
       <c r="AC82" t="inlineStr"/>
       <c r="AD82" t="inlineStr"/>
       <c r="AE82" t="inlineStr"/>
-      <c r="AF82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr">
+        <is>
+          <t>Sustainable Management of Underground Resources and Associated Infrastructure</t>
+        </is>
+      </c>
       <c r="AG82" t="inlineStr"/>
-      <c r="AH82" t="inlineStr"/>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr"/>
-      <c r="AK82" t="inlineStr"/>
-      <c r="AL82" t="inlineStr"/>
-      <c r="AM82" t="inlineStr"/>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>Sustainable Management of Underground Resources and Associated Infrastructure</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -12073,29 +11145,21 @@
       </c>
       <c r="Y83" t="inlineStr"/>
       <c r="Z83" t="inlineStr"/>
-      <c r="AA83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="inlineStr"/>
       <c r="AD83" t="inlineStr"/>
       <c r="AE83" t="inlineStr"/>
-      <c r="AF83" t="inlineStr"/>
+      <c r="AF83" t="inlineStr">
+        <is>
+          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
+        </is>
+      </c>
       <c r="AG83" t="inlineStr"/>
-      <c r="AH83" t="inlineStr"/>
-      <c r="AI83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr"/>
-      <c r="AK83" t="inlineStr"/>
-      <c r="AL83" t="inlineStr"/>
-      <c r="AM83" t="inlineStr"/>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>Support for the Advancement of the Energy Matrix Transition in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -12196,29 +11260,21 @@
       </c>
       <c r="Y84" t="inlineStr"/>
       <c r="Z84" t="inlineStr"/>
-      <c r="AA84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="inlineStr"/>
       <c r="AD84" t="inlineStr"/>
       <c r="AE84" t="inlineStr"/>
-      <c r="AF84" t="inlineStr"/>
+      <c r="AF84" t="inlineStr">
+        <is>
+          <t>Improving Transport Logistics and Competitiveness in Suriname</t>
+        </is>
+      </c>
       <c r="AG84" t="inlineStr"/>
-      <c r="AH84" t="inlineStr"/>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr"/>
-      <c r="AK84" t="inlineStr"/>
-      <c r="AL84" t="inlineStr"/>
-      <c r="AM84" t="inlineStr"/>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>Improving Transport Logistics and Competitiveness in Suriname</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -12319,29 +11375,21 @@
       </c>
       <c r="Y85" t="inlineStr"/>
       <c r="Z85" t="inlineStr"/>
-      <c r="AA85" t="inlineStr"/>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB85" t="inlineStr"/>
       <c r="AC85" t="inlineStr"/>
       <c r="AD85" t="inlineStr"/>
       <c r="AE85" t="inlineStr"/>
-      <c r="AF85" t="inlineStr"/>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>Health Care Network Strengthening in Guyana</t>
+        </is>
+      </c>
       <c r="AG85" t="inlineStr"/>
-      <c r="AH85" t="inlineStr"/>
-      <c r="AI85" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr"/>
-      <c r="AK85" t="inlineStr"/>
-      <c r="AL85" t="inlineStr"/>
-      <c r="AM85" t="inlineStr"/>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>Health Care Network Strengthening in Guyana</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -12442,29 +11490,21 @@
       </c>
       <c r="Y86" t="inlineStr"/>
       <c r="Z86" t="inlineStr"/>
-      <c r="AA86" t="inlineStr"/>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB86" t="inlineStr"/>
       <c r="AC86" t="inlineStr"/>
       <c r="AD86" t="inlineStr"/>
       <c r="AE86" t="inlineStr"/>
-      <c r="AF86" t="inlineStr"/>
+      <c r="AF86" t="inlineStr">
+        <is>
+          <t>Guyana Utility Scale Solar Photovoltaic Program (Guysol)</t>
+        </is>
+      </c>
       <c r="AG86" t="inlineStr"/>
-      <c r="AH86" t="inlineStr"/>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr"/>
-      <c r="AK86" t="inlineStr"/>
-      <c r="AL86" t="inlineStr"/>
-      <c r="AM86" t="inlineStr"/>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>Guyana Utility Scale Solar Photovoltaic Program (Guysol)</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -12565,29 +11605,21 @@
       </c>
       <c r="Y87" t="inlineStr"/>
       <c r="Z87" t="inlineStr"/>
-      <c r="AA87" t="inlineStr"/>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB87" t="inlineStr"/>
       <c r="AC87" t="inlineStr"/>
       <c r="AD87" t="inlineStr"/>
       <c r="AE87" t="inlineStr"/>
-      <c r="AF87" t="inlineStr"/>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>Health Care Network Strengthening in Guyana</t>
+        </is>
+      </c>
       <c r="AG87" t="inlineStr"/>
-      <c r="AH87" t="inlineStr"/>
-      <c r="AI87" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr"/>
-      <c r="AK87" t="inlineStr"/>
-      <c r="AL87" t="inlineStr"/>
-      <c r="AM87" t="inlineStr"/>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>Health Care Network Strengthening in Guyana</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -12688,29 +11720,21 @@
       </c>
       <c r="Y88" t="inlineStr"/>
       <c r="Z88" t="inlineStr"/>
-      <c r="AA88" t="inlineStr"/>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB88" t="inlineStr"/>
       <c r="AC88" t="inlineStr"/>
       <c r="AD88" t="inlineStr"/>
       <c r="AE88" t="inlineStr"/>
-      <c r="AF88" t="inlineStr"/>
+      <c r="AF88" t="inlineStr">
+        <is>
+          <t>Health Care Network Strengthening in Guyana</t>
+        </is>
+      </c>
       <c r="AG88" t="inlineStr"/>
-      <c r="AH88" t="inlineStr"/>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr"/>
-      <c r="AK88" t="inlineStr"/>
-      <c r="AL88" t="inlineStr"/>
-      <c r="AM88" t="inlineStr"/>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>Health Care Network Strengthening in Guyana</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -12811,29 +11835,21 @@
       </c>
       <c r="Y89" t="inlineStr"/>
       <c r="Z89" t="inlineStr"/>
-      <c r="AA89" t="inlineStr"/>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB89" t="inlineStr"/>
       <c r="AC89" t="inlineStr"/>
       <c r="AD89" t="inlineStr"/>
       <c r="AE89" t="inlineStr"/>
-      <c r="AF89" t="inlineStr"/>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>Support for the Health Systems Strengthening for the Prevention and Care Management of Non-Communicable Diseases Programme</t>
+        </is>
+      </c>
       <c r="AG89" t="inlineStr"/>
-      <c r="AH89" t="inlineStr"/>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr"/>
-      <c r="AK89" t="inlineStr"/>
-      <c r="AL89" t="inlineStr"/>
-      <c r="AM89" t="inlineStr"/>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>Support for the Health Systems Strengthening for the Prevention and Care Management of Non-Communicable Diseases Programme</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -12934,29 +11950,21 @@
       </c>
       <c r="Y90" t="inlineStr"/>
       <c r="Z90" t="inlineStr"/>
-      <c r="AA90" t="inlineStr"/>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr"/>
       <c r="AD90" t="inlineStr"/>
       <c r="AE90" t="inlineStr"/>
-      <c r="AF90" t="inlineStr"/>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>Guyana Utility Scale Solar Photovoltaic Program (Guysol)</t>
+        </is>
+      </c>
       <c r="AG90" t="inlineStr"/>
-      <c r="AH90" t="inlineStr"/>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr"/>
-      <c r="AK90" t="inlineStr"/>
-      <c r="AL90" t="inlineStr"/>
-      <c r="AM90" t="inlineStr"/>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>Guyana Utility Scale Solar Photovoltaic Program (Guysol)</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -13057,29 +12065,21 @@
       </c>
       <c r="Y91" t="inlineStr"/>
       <c r="Z91" t="inlineStr"/>
-      <c r="AA91" t="inlineStr"/>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB91" t="inlineStr"/>
       <c r="AC91" t="inlineStr"/>
       <c r="AD91" t="inlineStr"/>
       <c r="AE91" t="inlineStr"/>
-      <c r="AF91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>Road Network Upgrade and Expansion Program</t>
+        </is>
+      </c>
       <c r="AG91" t="inlineStr"/>
-      <c r="AH91" t="inlineStr"/>
-      <c r="AI91" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ91" t="inlineStr"/>
-      <c r="AK91" t="inlineStr"/>
-      <c r="AL91" t="inlineStr"/>
-      <c r="AM91" t="inlineStr"/>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>Road Network Upgrade and Expansion Program</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -13180,29 +12180,21 @@
       </c>
       <c r="Y92" t="inlineStr"/>
       <c r="Z92" t="inlineStr"/>
-      <c r="AA92" t="inlineStr"/>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB92" t="inlineStr"/>
       <c r="AC92" t="inlineStr"/>
       <c r="AD92" t="inlineStr"/>
       <c r="AE92" t="inlineStr"/>
-      <c r="AF92" t="inlineStr"/>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>Program to Support Climate Resilient Road Infrastructure Development</t>
+        </is>
+      </c>
       <c r="AG92" t="inlineStr"/>
-      <c r="AH92" t="inlineStr"/>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr"/>
-      <c r="AK92" t="inlineStr"/>
-      <c r="AL92" t="inlineStr"/>
-      <c r="AM92" t="inlineStr"/>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>Program to Support Climate Resilient Road Infrastructure Development</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -13303,29 +12295,21 @@
       </c>
       <c r="Y93" t="inlineStr"/>
       <c r="Z93" t="inlineStr"/>
-      <c r="AA93" t="inlineStr"/>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB93" t="inlineStr"/>
       <c r="AC93" t="inlineStr"/>
       <c r="AD93" t="inlineStr"/>
       <c r="AE93" t="inlineStr"/>
-      <c r="AF93" t="inlineStr"/>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>Multipurpose Water Supply and Irrigation Program For the Municipios of Batallas</t>
+        </is>
+      </c>
       <c r="AG93" t="inlineStr"/>
-      <c r="AH93" t="inlineStr"/>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ93" t="inlineStr"/>
-      <c r="AK93" t="inlineStr"/>
-      <c r="AL93" t="inlineStr"/>
-      <c r="AM93" t="inlineStr"/>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>Multipurpose Water Supply and Irrigation Program For the Municipios of Batallas</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -13426,29 +12410,21 @@
       </c>
       <c r="Y94" t="inlineStr"/>
       <c r="Z94" t="inlineStr"/>
-      <c r="AA94" t="inlineStr"/>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB94" t="inlineStr"/>
       <c r="AC94" t="inlineStr"/>
       <c r="AD94" t="inlineStr"/>
       <c r="AE94" t="inlineStr"/>
-      <c r="AF94" t="inlineStr"/>
+      <c r="AF94" t="inlineStr">
+        <is>
+          <t>Multipurpose Water Supply and Irrigation Program For the Municipios of Batallas</t>
+        </is>
+      </c>
       <c r="AG94" t="inlineStr"/>
-      <c r="AH94" t="inlineStr"/>
-      <c r="AI94" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ94" t="inlineStr"/>
-      <c r="AK94" t="inlineStr"/>
-      <c r="AL94" t="inlineStr"/>
-      <c r="AM94" t="inlineStr"/>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>Multipurpose Water Supply and Irrigation Program For the Municipios of Batallas</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -13549,29 +12525,21 @@
       </c>
       <c r="Y95" t="inlineStr"/>
       <c r="Z95" t="inlineStr"/>
-      <c r="AA95" t="inlineStr"/>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB95" t="inlineStr"/>
       <c r="AC95" t="inlineStr"/>
       <c r="AD95" t="inlineStr"/>
       <c r="AE95" t="inlineStr"/>
-      <c r="AF95" t="inlineStr"/>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program II</t>
+        </is>
+      </c>
       <c r="AG95" t="inlineStr"/>
-      <c r="AH95" t="inlineStr"/>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr"/>
-      <c r="AK95" t="inlineStr"/>
-      <c r="AL95" t="inlineStr"/>
-      <c r="AM95" t="inlineStr"/>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program II</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -13668,29 +12636,21 @@
       </c>
       <c r="Y96" t="inlineStr"/>
       <c r="Z96" t="inlineStr"/>
-      <c r="AA96" t="inlineStr"/>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr"/>
       <c r="AD96" t="inlineStr"/>
       <c r="AE96" t="inlineStr"/>
-      <c r="AF96" t="inlineStr"/>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>Private Sector Development through Investment Promotion</t>
+        </is>
+      </c>
       <c r="AG96" t="inlineStr"/>
-      <c r="AH96" t="inlineStr"/>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ96" t="inlineStr"/>
-      <c r="AK96" t="inlineStr"/>
-      <c r="AL96" t="inlineStr"/>
-      <c r="AM96" t="inlineStr"/>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>Private Sector Development through Investment Promotion</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -13791,29 +12751,21 @@
       </c>
       <c r="Y97" t="inlineStr"/>
       <c r="Z97" t="inlineStr"/>
-      <c r="AA97" t="inlineStr"/>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB97" t="inlineStr"/>
       <c r="AC97" t="inlineStr"/>
       <c r="AD97" t="inlineStr"/>
       <c r="AE97" t="inlineStr"/>
-      <c r="AF97" t="inlineStr"/>
+      <c r="AF97" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG97" t="inlineStr"/>
-      <c r="AH97" t="inlineStr"/>
-      <c r="AI97" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ97" t="inlineStr"/>
-      <c r="AK97" t="inlineStr"/>
-      <c r="AL97" t="inlineStr"/>
-      <c r="AM97" t="inlineStr"/>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -13910,29 +12862,21 @@
       </c>
       <c r="Y98" t="inlineStr"/>
       <c r="Z98" t="inlineStr"/>
-      <c r="AA98" t="inlineStr"/>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB98" t="inlineStr"/>
       <c r="AC98" t="inlineStr"/>
       <c r="AD98" t="inlineStr"/>
       <c r="AE98" t="inlineStr"/>
-      <c r="AF98" t="inlineStr"/>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>Competitiveness and Trade</t>
+        </is>
+      </c>
       <c r="AG98" t="inlineStr"/>
-      <c r="AH98" t="inlineStr"/>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr"/>
-      <c r="AK98" t="inlineStr"/>
-      <c r="AL98" t="inlineStr"/>
-      <c r="AM98" t="inlineStr"/>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>Competitiveness and Trade</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -14033,29 +12977,21 @@
       </c>
       <c r="Y99" t="inlineStr"/>
       <c r="Z99" t="inlineStr"/>
-      <c r="AA99" t="inlineStr"/>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB99" t="inlineStr"/>
       <c r="AC99" t="inlineStr"/>
       <c r="AD99" t="inlineStr"/>
       <c r="AE99" t="inlineStr"/>
-      <c r="AF99" t="inlineStr"/>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG99" t="inlineStr"/>
-      <c r="AH99" t="inlineStr"/>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr"/>
-      <c r="AK99" t="inlineStr"/>
-      <c r="AL99" t="inlineStr"/>
-      <c r="AM99" t="inlineStr"/>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -14152,29 +13088,21 @@
       </c>
       <c r="Y100" t="inlineStr"/>
       <c r="Z100" t="inlineStr"/>
-      <c r="AA100" t="inlineStr"/>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB100" t="inlineStr"/>
       <c r="AC100" t="inlineStr"/>
       <c r="AD100" t="inlineStr"/>
       <c r="AE100" t="inlineStr"/>
-      <c r="AF100" t="inlineStr"/>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>Private Sector Development through Investment Promotion</t>
+        </is>
+      </c>
       <c r="AG100" t="inlineStr"/>
-      <c r="AH100" t="inlineStr"/>
-      <c r="AI100" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ100" t="inlineStr"/>
-      <c r="AK100" t="inlineStr"/>
-      <c r="AL100" t="inlineStr"/>
-      <c r="AM100" t="inlineStr"/>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>Private Sector Development through Investment Promotion</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -14275,29 +13203,21 @@
       </c>
       <c r="Y101" t="inlineStr"/>
       <c r="Z101" t="inlineStr"/>
-      <c r="AA101" t="inlineStr"/>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB101" t="inlineStr"/>
       <c r="AC101" t="inlineStr"/>
       <c r="AD101" t="inlineStr"/>
       <c r="AE101" t="inlineStr"/>
-      <c r="AF101" t="inlineStr"/>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG101" t="inlineStr"/>
-      <c r="AH101" t="inlineStr"/>
-      <c r="AI101" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ101" t="inlineStr"/>
-      <c r="AK101" t="inlineStr"/>
-      <c r="AL101" t="inlineStr"/>
-      <c r="AM101" t="inlineStr"/>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -14394,29 +13314,21 @@
       </c>
       <c r="Y102" t="inlineStr"/>
       <c r="Z102" t="inlineStr"/>
-      <c r="AA102" t="inlineStr"/>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB102" t="inlineStr"/>
       <c r="AC102" t="inlineStr"/>
       <c r="AD102" t="inlineStr"/>
       <c r="AE102" t="inlineStr"/>
-      <c r="AF102" t="inlineStr"/>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>Public Sector Efficiency Program</t>
+        </is>
+      </c>
       <c r="AG102" t="inlineStr"/>
-      <c r="AH102" t="inlineStr"/>
-      <c r="AI102" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ102" t="inlineStr"/>
-      <c r="AK102" t="inlineStr"/>
-      <c r="AL102" t="inlineStr"/>
-      <c r="AM102" t="inlineStr"/>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>Public Sector Efficiency Program</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -14517,29 +13429,21 @@
       </c>
       <c r="Y103" t="inlineStr"/>
       <c r="Z103" t="inlineStr"/>
-      <c r="AA103" t="inlineStr"/>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB103" t="inlineStr"/>
       <c r="AC103" t="inlineStr"/>
       <c r="AD103" t="inlineStr"/>
       <c r="AE103" t="inlineStr"/>
-      <c r="AF103" t="inlineStr"/>
+      <c r="AF103" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG103" t="inlineStr"/>
-      <c r="AH103" t="inlineStr"/>
-      <c r="AI103" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ103" t="inlineStr"/>
-      <c r="AK103" t="inlineStr"/>
-      <c r="AL103" t="inlineStr"/>
-      <c r="AM103" t="inlineStr"/>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -14640,29 +13544,21 @@
       </c>
       <c r="Y104" t="inlineStr"/>
       <c r="Z104" t="inlineStr"/>
-      <c r="AA104" t="inlineStr"/>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB104" t="inlineStr"/>
       <c r="AC104" t="inlineStr"/>
       <c r="AD104" t="inlineStr"/>
       <c r="AE104" t="inlineStr"/>
-      <c r="AF104" t="inlineStr"/>
+      <c r="AF104" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG104" t="inlineStr"/>
-      <c r="AH104" t="inlineStr"/>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr"/>
-      <c r="AK104" t="inlineStr"/>
-      <c r="AL104" t="inlineStr"/>
-      <c r="AM104" t="inlineStr"/>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -14763,29 +13659,21 @@
       </c>
       <c r="Y105" t="inlineStr"/>
       <c r="Z105" t="inlineStr"/>
-      <c r="AA105" t="inlineStr"/>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB105" t="inlineStr"/>
       <c r="AC105" t="inlineStr"/>
       <c r="AD105" t="inlineStr"/>
       <c r="AE105" t="inlineStr"/>
-      <c r="AF105" t="inlineStr"/>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program II</t>
+        </is>
+      </c>
       <c r="AG105" t="inlineStr"/>
-      <c r="AH105" t="inlineStr"/>
-      <c r="AI105" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ105" t="inlineStr"/>
-      <c r="AK105" t="inlineStr"/>
-      <c r="AL105" t="inlineStr"/>
-      <c r="AM105" t="inlineStr"/>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program II</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -14886,29 +13774,21 @@
       </c>
       <c r="Y106" t="inlineStr"/>
       <c r="Z106" t="inlineStr"/>
-      <c r="AA106" t="inlineStr"/>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB106" t="inlineStr"/>
       <c r="AC106" t="inlineStr"/>
       <c r="AD106" t="inlineStr"/>
       <c r="AE106" t="inlineStr"/>
-      <c r="AF106" t="inlineStr"/>
+      <c r="AF106" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program II</t>
+        </is>
+      </c>
       <c r="AG106" t="inlineStr"/>
-      <c r="AH106" t="inlineStr"/>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ106" t="inlineStr"/>
-      <c r="AK106" t="inlineStr"/>
-      <c r="AL106" t="inlineStr"/>
-      <c r="AM106" t="inlineStr"/>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program II</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -15009,29 +13889,21 @@
       </c>
       <c r="Y107" t="inlineStr"/>
       <c r="Z107" t="inlineStr"/>
-      <c r="AA107" t="inlineStr"/>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr"/>
       <c r="AD107" t="inlineStr"/>
       <c r="AE107" t="inlineStr"/>
-      <c r="AF107" t="inlineStr"/>
+      <c r="AF107" t="inlineStr">
+        <is>
+          <t>Power Sector Development Program 2012-2016 (Reventazon Hydroelectric Project)</t>
+        </is>
+      </c>
       <c r="AG107" t="inlineStr"/>
-      <c r="AH107" t="inlineStr"/>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr"/>
-      <c r="AK107" t="inlineStr"/>
-      <c r="AL107" t="inlineStr"/>
-      <c r="AM107" t="inlineStr"/>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>Power Sector Development Program 2012-2016 (Reventazon Hydroelectric Project)</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -15132,29 +14004,21 @@
       </c>
       <c r="Y108" t="inlineStr"/>
       <c r="Z108" t="inlineStr"/>
-      <c r="AA108" t="inlineStr"/>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr"/>
       <c r="AD108" t="inlineStr"/>
       <c r="AE108" t="inlineStr"/>
-      <c r="AF108" t="inlineStr"/>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG108" t="inlineStr"/>
-      <c r="AH108" t="inlineStr"/>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ108" t="inlineStr"/>
-      <c r="AK108" t="inlineStr"/>
-      <c r="AL108" t="inlineStr"/>
-      <c r="AM108" t="inlineStr"/>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -15255,29 +14119,21 @@
       </c>
       <c r="Y109" t="inlineStr"/>
       <c r="Z109" t="inlineStr"/>
-      <c r="AA109" t="inlineStr"/>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB109" t="inlineStr"/>
       <c r="AC109" t="inlineStr"/>
       <c r="AD109" t="inlineStr"/>
       <c r="AE109" t="inlineStr"/>
-      <c r="AF109" t="inlineStr"/>
+      <c r="AF109" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG109" t="inlineStr"/>
-      <c r="AH109" t="inlineStr"/>
-      <c r="AI109" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ109" t="inlineStr"/>
-      <c r="AK109" t="inlineStr"/>
-      <c r="AL109" t="inlineStr"/>
-      <c r="AM109" t="inlineStr"/>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -15374,29 +14230,21 @@
       </c>
       <c r="Y110" t="inlineStr"/>
       <c r="Z110" t="inlineStr"/>
-      <c r="AA110" t="inlineStr"/>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr"/>
       <c r="AD110" t="inlineStr"/>
       <c r="AE110" t="inlineStr"/>
-      <c r="AF110" t="inlineStr"/>
+      <c r="AF110" t="inlineStr">
+        <is>
+          <t>Private Sector Development through Investment Promotion</t>
+        </is>
+      </c>
       <c r="AG110" t="inlineStr"/>
-      <c r="AH110" t="inlineStr"/>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr"/>
-      <c r="AK110" t="inlineStr"/>
-      <c r="AL110" t="inlineStr"/>
-      <c r="AM110" t="inlineStr"/>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>Private Sector Development through Investment Promotion</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -15493,29 +14341,21 @@
       </c>
       <c r="Y111" t="inlineStr"/>
       <c r="Z111" t="inlineStr"/>
-      <c r="AA111" t="inlineStr"/>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr"/>
       <c r="AD111" t="inlineStr"/>
       <c r="AE111" t="inlineStr"/>
-      <c r="AF111" t="inlineStr"/>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>Private Sector Development through Investment Promotion</t>
+        </is>
+      </c>
       <c r="AG111" t="inlineStr"/>
-      <c r="AH111" t="inlineStr"/>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr"/>
-      <c r="AK111" t="inlineStr"/>
-      <c r="AL111" t="inlineStr"/>
-      <c r="AM111" t="inlineStr"/>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>Private Sector Development through Investment Promotion</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -15616,29 +14456,21 @@
       </c>
       <c r="Y112" t="inlineStr"/>
       <c r="Z112" t="inlineStr"/>
-      <c r="AA112" t="inlineStr"/>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr"/>
       <c r="AD112" t="inlineStr"/>
       <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ112" t="inlineStr"/>
-      <c r="AK112" t="inlineStr"/>
-      <c r="AL112" t="inlineStr"/>
-      <c r="AM112" t="inlineStr"/>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -15739,29 +14571,21 @@
       </c>
       <c r="Y113" t="inlineStr"/>
       <c r="Z113" t="inlineStr"/>
-      <c r="AA113" t="inlineStr"/>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr"/>
       <c r="AD113" t="inlineStr"/>
       <c r="AE113" t="inlineStr"/>
-      <c r="AF113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr">
+        <is>
+          <t>First Electric Power Sector Development Program 2008-2011</t>
+        </is>
+      </c>
       <c r="AG113" t="inlineStr"/>
-      <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr"/>
-      <c r="AK113" t="inlineStr"/>
-      <c r="AL113" t="inlineStr"/>
-      <c r="AM113" t="inlineStr"/>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>First Electric Power Sector Development Program 2008-2011</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -15862,29 +14686,21 @@
       </c>
       <c r="Y114" t="inlineStr"/>
       <c r="Z114" t="inlineStr"/>
-      <c r="AA114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr"/>
       <c r="AD114" t="inlineStr"/>
       <c r="AE114" t="inlineStr"/>
-      <c r="AF114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG114" t="inlineStr"/>
-      <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ114" t="inlineStr"/>
-      <c r="AK114" t="inlineStr"/>
-      <c r="AL114" t="inlineStr"/>
-      <c r="AM114" t="inlineStr"/>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -15985,29 +14801,21 @@
       </c>
       <c r="Y115" t="inlineStr"/>
       <c r="Z115" t="inlineStr"/>
-      <c r="AA115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB115" t="inlineStr"/>
       <c r="AC115" t="inlineStr"/>
       <c r="AD115" t="inlineStr"/>
       <c r="AE115" t="inlineStr"/>
-      <c r="AF115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG115" t="inlineStr"/>
-      <c r="AH115" t="inlineStr"/>
-      <c r="AI115" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr"/>
-      <c r="AK115" t="inlineStr"/>
-      <c r="AL115" t="inlineStr"/>
-      <c r="AM115" t="inlineStr"/>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -16108,29 +14916,21 @@
       </c>
       <c r="Y116" t="inlineStr"/>
       <c r="Z116" t="inlineStr"/>
-      <c r="AA116" t="inlineStr"/>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB116" t="inlineStr"/>
       <c r="AC116" t="inlineStr"/>
       <c r="AD116" t="inlineStr"/>
       <c r="AE116" t="inlineStr"/>
-      <c r="AF116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program II</t>
+        </is>
+      </c>
       <c r="AG116" t="inlineStr"/>
-      <c r="AH116" t="inlineStr"/>
-      <c r="AI116" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr"/>
-      <c r="AK116" t="inlineStr"/>
-      <c r="AL116" t="inlineStr"/>
-      <c r="AM116" t="inlineStr"/>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program II</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -16231,29 +15031,21 @@
       </c>
       <c r="Y117" t="inlineStr"/>
       <c r="Z117" t="inlineStr"/>
-      <c r="AA117" t="inlineStr"/>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB117" t="inlineStr"/>
       <c r="AC117" t="inlineStr"/>
       <c r="AD117" t="inlineStr"/>
       <c r="AE117" t="inlineStr"/>
-      <c r="AF117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG117" t="inlineStr"/>
-      <c r="AH117" t="inlineStr"/>
-      <c r="AI117" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ117" t="inlineStr"/>
-      <c r="AK117" t="inlineStr"/>
-      <c r="AL117" t="inlineStr"/>
-      <c r="AM117" t="inlineStr"/>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -16354,29 +15146,21 @@
       </c>
       <c r="Y118" t="inlineStr"/>
       <c r="Z118" t="inlineStr"/>
-      <c r="AA118" t="inlineStr"/>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB118" t="inlineStr"/>
       <c r="AC118" t="inlineStr"/>
       <c r="AD118" t="inlineStr"/>
       <c r="AE118" t="inlineStr"/>
-      <c r="AF118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr">
+        <is>
+          <t>Support for the Transmission System in Paraguay</t>
+        </is>
+      </c>
       <c r="AG118" t="inlineStr"/>
-      <c r="AH118" t="inlineStr"/>
-      <c r="AI118" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ118" t="inlineStr"/>
-      <c r="AK118" t="inlineStr"/>
-      <c r="AL118" t="inlineStr"/>
-      <c r="AM118" t="inlineStr"/>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>Support for the Transmission System in Paraguay</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -16477,29 +15261,21 @@
       </c>
       <c r="Y119" t="inlineStr"/>
       <c r="Z119" t="inlineStr"/>
-      <c r="AA119" t="inlineStr"/>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB119" t="inlineStr"/>
       <c r="AC119" t="inlineStr"/>
       <c r="AD119" t="inlineStr"/>
       <c r="AE119" t="inlineStr"/>
-      <c r="AF119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program</t>
+        </is>
+      </c>
       <c r="AG119" t="inlineStr"/>
-      <c r="AH119" t="inlineStr"/>
-      <c r="AI119" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ119" t="inlineStr"/>
-      <c r="AK119" t="inlineStr"/>
-      <c r="AL119" t="inlineStr"/>
-      <c r="AM119" t="inlineStr"/>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -16600,29 +15376,21 @@
       </c>
       <c r="Y120" t="inlineStr"/>
       <c r="Z120" t="inlineStr"/>
-      <c r="AA120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB120" t="inlineStr"/>
       <c r="AC120" t="inlineStr"/>
       <c r="AD120" t="inlineStr"/>
       <c r="AE120" t="inlineStr"/>
-      <c r="AF120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr">
+        <is>
+          <t>Rural Electrification Program II</t>
+        </is>
+      </c>
       <c r="AG120" t="inlineStr"/>
-      <c r="AH120" t="inlineStr"/>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr"/>
-      <c r="AK120" t="inlineStr"/>
-      <c r="AL120" t="inlineStr"/>
-      <c r="AM120" t="inlineStr"/>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>Rural Electrification Program II</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -16719,29 +15487,21 @@
       </c>
       <c r="Y121" t="inlineStr"/>
       <c r="Z121" t="inlineStr"/>
-      <c r="AA121" t="inlineStr"/>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB121" t="inlineStr"/>
       <c r="AC121" t="inlineStr"/>
       <c r="AD121" t="inlineStr"/>
       <c r="AE121" t="inlineStr"/>
-      <c r="AF121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>Support to the transmission program in Ecuador</t>
+        </is>
+      </c>
       <c r="AG121" t="inlineStr"/>
-      <c r="AH121" t="inlineStr"/>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ121" t="inlineStr"/>
-      <c r="AK121" t="inlineStr"/>
-      <c r="AL121" t="inlineStr"/>
-      <c r="AM121" t="inlineStr"/>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>Support to the transmission program in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -16842,29 +15602,21 @@
       </c>
       <c r="Y122" t="inlineStr"/>
       <c r="Z122" t="inlineStr"/>
-      <c r="AA122" t="inlineStr"/>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB122" t="inlineStr"/>
       <c r="AC122" t="inlineStr"/>
       <c r="AD122" t="inlineStr"/>
       <c r="AE122" t="inlineStr"/>
-      <c r="AF122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr">
+        <is>
+          <t>Support to the Action Social Center of Music Program. Phase II</t>
+        </is>
+      </c>
       <c r="AG122" t="inlineStr"/>
-      <c r="AH122" t="inlineStr"/>
-      <c r="AI122" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ122" t="inlineStr"/>
-      <c r="AK122" t="inlineStr"/>
-      <c r="AL122" t="inlineStr"/>
-      <c r="AM122" t="inlineStr"/>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>Support to the Action Social Center of Music Program. Phase II</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -16965,29 +15717,21 @@
       </c>
       <c r="Y123" t="inlineStr"/>
       <c r="Z123" t="inlineStr"/>
-      <c r="AA123" t="inlineStr"/>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB123" t="inlineStr"/>
       <c r="AC123" t="inlineStr"/>
       <c r="AD123" t="inlineStr"/>
       <c r="AE123" t="inlineStr"/>
-      <c r="AF123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr">
+        <is>
+          <t>Rehabilitation of Road Infrastructure for Integration of the Territory</t>
+        </is>
+      </c>
       <c r="AG123" t="inlineStr"/>
-      <c r="AH123" t="inlineStr"/>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr"/>
-      <c r="AK123" t="inlineStr"/>
-      <c r="AL123" t="inlineStr"/>
-      <c r="AM123" t="inlineStr"/>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>Rehabilitation of Road Infrastructure for Integration of the Territory</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -17088,29 +15832,21 @@
       </c>
       <c r="Y124" t="inlineStr"/>
       <c r="Z124" t="inlineStr"/>
-      <c r="AA124" t="inlineStr"/>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB124" t="inlineStr"/>
       <c r="AC124" t="inlineStr"/>
       <c r="AD124" t="inlineStr"/>
       <c r="AE124" t="inlineStr"/>
-      <c r="AF124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG124" t="inlineStr"/>
-      <c r="AH124" t="inlineStr"/>
-      <c r="AI124" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ124" t="inlineStr"/>
-      <c r="AK124" t="inlineStr"/>
-      <c r="AL124" t="inlineStr"/>
-      <c r="AM124" t="inlineStr"/>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -17211,29 +15947,21 @@
       </c>
       <c r="Y125" t="inlineStr"/>
       <c r="Z125" t="inlineStr"/>
-      <c r="AA125" t="inlineStr"/>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB125" t="inlineStr"/>
       <c r="AC125" t="inlineStr"/>
       <c r="AD125" t="inlineStr"/>
       <c r="AE125" t="inlineStr"/>
-      <c r="AF125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG125" t="inlineStr"/>
-      <c r="AH125" t="inlineStr"/>
-      <c r="AI125" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ125" t="inlineStr"/>
-      <c r="AK125" t="inlineStr"/>
-      <c r="AL125" t="inlineStr"/>
-      <c r="AM125" t="inlineStr"/>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -17334,29 +16062,21 @@
       </c>
       <c r="Y126" t="inlineStr"/>
       <c r="Z126" t="inlineStr"/>
-      <c r="AA126" t="inlineStr"/>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr"/>
       <c r="AD126" t="inlineStr"/>
       <c r="AE126" t="inlineStr"/>
-      <c r="AF126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr">
+        <is>
+          <t>First Electric Power Sector Development Program 2008-2011</t>
+        </is>
+      </c>
       <c r="AG126" t="inlineStr"/>
-      <c r="AH126" t="inlineStr"/>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr"/>
-      <c r="AK126" t="inlineStr"/>
-      <c r="AL126" t="inlineStr"/>
-      <c r="AM126" t="inlineStr"/>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>First Electric Power Sector Development Program 2008-2011</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -17457,29 +16177,21 @@
       </c>
       <c r="Y127" t="inlineStr"/>
       <c r="Z127" t="inlineStr"/>
-      <c r="AA127" t="inlineStr"/>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr"/>
       <c r="AD127" t="inlineStr"/>
       <c r="AE127" t="inlineStr"/>
-      <c r="AF127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>WASA Modernization and Wastewater Infrastructure Rehabilitation Program</t>
+        </is>
+      </c>
       <c r="AG127" t="inlineStr"/>
-      <c r="AH127" t="inlineStr"/>
-      <c r="AI127" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ127" t="inlineStr"/>
-      <c r="AK127" t="inlineStr"/>
-      <c r="AL127" t="inlineStr"/>
-      <c r="AM127" t="inlineStr"/>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>WASA Modernization and Wastewater Infrastructure Rehabilitation Program</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -17580,29 +16292,21 @@
       </c>
       <c r="Y128" t="inlineStr"/>
       <c r="Z128" t="inlineStr"/>
-      <c r="AA128" t="inlineStr"/>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB128" t="inlineStr"/>
       <c r="AC128" t="inlineStr"/>
       <c r="AD128" t="inlineStr"/>
       <c r="AE128" t="inlineStr"/>
-      <c r="AF128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr">
+        <is>
+          <t>Cochabamba - La Paz Transmission Line</t>
+        </is>
+      </c>
       <c r="AG128" t="inlineStr"/>
-      <c r="AH128" t="inlineStr"/>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ128" t="inlineStr"/>
-      <c r="AK128" t="inlineStr"/>
-      <c r="AL128" t="inlineStr"/>
-      <c r="AM128" t="inlineStr"/>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>Cochabamba - La Paz Transmission Line</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -17703,29 +16407,21 @@
       </c>
       <c r="Y129" t="inlineStr"/>
       <c r="Z129" t="inlineStr"/>
-      <c r="AA129" t="inlineStr"/>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr"/>
       <c r="AD129" t="inlineStr"/>
       <c r="AE129" t="inlineStr"/>
-      <c r="AF129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr">
+        <is>
+          <t>Program for the Expansion and Improvement of Specialized Health Care in the State of Ceará II – PROEXMAES II</t>
+        </is>
+      </c>
       <c r="AG129" t="inlineStr"/>
-      <c r="AH129" t="inlineStr"/>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr"/>
-      <c r="AK129" t="inlineStr"/>
-      <c r="AL129" t="inlineStr"/>
-      <c r="AM129" t="inlineStr"/>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>Program for the Expansion and Improvement of Specialized Health Care in the State of Ceará II – PROEXMAES II</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -17826,29 +16522,21 @@
       </c>
       <c r="Y130" t="inlineStr"/>
       <c r="Z130" t="inlineStr"/>
-      <c r="AA130" t="inlineStr"/>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr"/>
       <c r="AD130" t="inlineStr"/>
       <c r="AE130" t="inlineStr"/>
-      <c r="AF130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>Power Sector Development Program 2012-2016 (Reventazon Hydroelectric Project)</t>
+        </is>
+      </c>
       <c r="AG130" t="inlineStr"/>
-      <c r="AH130" t="inlineStr"/>
-      <c r="AI130" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ130" t="inlineStr"/>
-      <c r="AK130" t="inlineStr"/>
-      <c r="AL130" t="inlineStr"/>
-      <c r="AM130" t="inlineStr"/>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>Power Sector Development Program 2012-2016 (Reventazon Hydroelectric Project)</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -17949,29 +16637,21 @@
       </c>
       <c r="Y131" t="inlineStr"/>
       <c r="Z131" t="inlineStr"/>
-      <c r="AA131" t="inlineStr"/>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr"/>
       <c r="AD131" t="inlineStr"/>
       <c r="AE131" t="inlineStr"/>
-      <c r="AF131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr">
+        <is>
+          <t>Program for the Expansion and Improvement of Specialized Health Care in the State of Ceará II – PROEXMAES II</t>
+        </is>
+      </c>
       <c r="AG131" t="inlineStr"/>
-      <c r="AH131" t="inlineStr"/>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ131" t="inlineStr"/>
-      <c r="AK131" t="inlineStr"/>
-      <c r="AL131" t="inlineStr"/>
-      <c r="AM131" t="inlineStr"/>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>Program for the Expansion and Improvement of Specialized Health Care in the State of Ceará II – PROEXMAES II</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -18072,29 +16752,21 @@
       </c>
       <c r="Y132" t="inlineStr"/>
       <c r="Z132" t="inlineStr"/>
-      <c r="AA132" t="inlineStr"/>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr"/>
       <c r="AD132" t="inlineStr"/>
       <c r="AE132" t="inlineStr"/>
-      <c r="AF132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr">
+        <is>
+          <t>Water Supply and Sanitation Infrastructure Improvement Program</t>
+        </is>
+      </c>
       <c r="AG132" t="inlineStr"/>
-      <c r="AH132" t="inlineStr"/>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ132" t="inlineStr"/>
-      <c r="AK132" t="inlineStr"/>
-      <c r="AL132" t="inlineStr"/>
-      <c r="AM132" t="inlineStr"/>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>Water Supply and Sanitation Infrastructure Improvement Program</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -18195,29 +16867,21 @@
       </c>
       <c r="Y133" t="inlineStr"/>
       <c r="Z133" t="inlineStr"/>
-      <c r="AA133" t="inlineStr"/>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB133" t="inlineStr"/>
       <c r="AC133" t="inlineStr"/>
       <c r="AD133" t="inlineStr"/>
       <c r="AE133" t="inlineStr"/>
-      <c r="AF133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr">
+        <is>
+          <t>Power Utility Upgrade Program</t>
+        </is>
+      </c>
       <c r="AG133" t="inlineStr"/>
-      <c r="AH133" t="inlineStr"/>
-      <c r="AI133" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ133" t="inlineStr"/>
-      <c r="AK133" t="inlineStr"/>
-      <c r="AL133" t="inlineStr"/>
-      <c r="AM133" t="inlineStr"/>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>Power Utility Upgrade Program</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -18318,29 +16982,21 @@
       </c>
       <c r="Y134" t="inlineStr"/>
       <c r="Z134" t="inlineStr"/>
-      <c r="AA134" t="inlineStr"/>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr"/>
       <c r="AD134" t="inlineStr"/>
       <c r="AE134" t="inlineStr"/>
-      <c r="AF134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr">
+        <is>
+          <t>Power Utility Upgrade Program</t>
+        </is>
+      </c>
       <c r="AG134" t="inlineStr"/>
-      <c r="AH134" t="inlineStr"/>
-      <c r="AI134" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ134" t="inlineStr"/>
-      <c r="AK134" t="inlineStr"/>
-      <c r="AL134" t="inlineStr"/>
-      <c r="AM134" t="inlineStr"/>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>Power Utility Upgrade Program</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -18441,29 +17097,21 @@
       </c>
       <c r="Y135" t="inlineStr"/>
       <c r="Z135" t="inlineStr"/>
-      <c r="AA135" t="inlineStr"/>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB135" t="inlineStr"/>
       <c r="AC135" t="inlineStr"/>
       <c r="AD135" t="inlineStr"/>
       <c r="AE135" t="inlineStr"/>
-      <c r="AF135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr">
+        <is>
+          <t>Support for Haiti's Transportation Sector III</t>
+        </is>
+      </c>
       <c r="AG135" t="inlineStr"/>
-      <c r="AH135" t="inlineStr"/>
-      <c r="AI135" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ135" t="inlineStr"/>
-      <c r="AK135" t="inlineStr"/>
-      <c r="AL135" t="inlineStr"/>
-      <c r="AM135" t="inlineStr"/>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>Support for Haiti's Transportation Sector III</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -18564,29 +17212,21 @@
       </c>
       <c r="Y136" t="inlineStr"/>
       <c r="Z136" t="inlineStr"/>
-      <c r="AA136" t="inlineStr"/>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr"/>
       <c r="AD136" t="inlineStr"/>
       <c r="AE136" t="inlineStr"/>
-      <c r="AF136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr">
+        <is>
+          <t>Support to the transmission program in Ecuador</t>
+        </is>
+      </c>
       <c r="AG136" t="inlineStr"/>
-      <c r="AH136" t="inlineStr"/>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr"/>
-      <c r="AK136" t="inlineStr"/>
-      <c r="AL136" t="inlineStr"/>
-      <c r="AM136" t="inlineStr"/>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>Support to the transmission program in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -18687,29 +17327,21 @@
       </c>
       <c r="Y137" t="inlineStr"/>
       <c r="Z137" t="inlineStr"/>
-      <c r="AA137" t="inlineStr"/>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr"/>
       <c r="AD137" t="inlineStr"/>
       <c r="AE137" t="inlineStr"/>
-      <c r="AF137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>Support to the transmission program in Ecuador</t>
+        </is>
+      </c>
       <c r="AG137" t="inlineStr"/>
-      <c r="AH137" t="inlineStr"/>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ137" t="inlineStr"/>
-      <c r="AK137" t="inlineStr"/>
-      <c r="AL137" t="inlineStr"/>
-      <c r="AM137" t="inlineStr"/>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>Support to the transmission program in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -18810,29 +17442,21 @@
       </c>
       <c r="Y138" t="inlineStr"/>
       <c r="Z138" t="inlineStr"/>
-      <c r="AA138" t="inlineStr"/>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB138" t="inlineStr"/>
       <c r="AC138" t="inlineStr"/>
       <c r="AD138" t="inlineStr"/>
       <c r="AE138" t="inlineStr"/>
-      <c r="AF138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>Investment Plan to Support the Transition of the Energy Matrix in Ecuador</t>
+        </is>
+      </c>
       <c r="AG138" t="inlineStr"/>
-      <c r="AH138" t="inlineStr"/>
-      <c r="AI138" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ138" t="inlineStr"/>
-      <c r="AK138" t="inlineStr"/>
-      <c r="AL138" t="inlineStr"/>
-      <c r="AM138" t="inlineStr"/>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>Investment Plan to Support the Transition of the Energy Matrix in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -18933,29 +17557,21 @@
       </c>
       <c r="Y139" t="inlineStr"/>
       <c r="Z139" t="inlineStr"/>
-      <c r="AA139" t="inlineStr"/>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr"/>
       <c r="AD139" t="inlineStr"/>
       <c r="AE139" t="inlineStr"/>
-      <c r="AF139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>Support to the transmission program in Ecuador</t>
+        </is>
+      </c>
       <c r="AG139" t="inlineStr"/>
-      <c r="AH139" t="inlineStr"/>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr"/>
-      <c r="AK139" t="inlineStr"/>
-      <c r="AL139" t="inlineStr"/>
-      <c r="AM139" t="inlineStr"/>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>Support to the transmission program in Ecuador</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -19056,29 +17672,21 @@
       </c>
       <c r="Y140" t="inlineStr"/>
       <c r="Z140" t="inlineStr"/>
-      <c r="AA140" t="inlineStr"/>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB140" t="inlineStr"/>
       <c r="AC140" t="inlineStr"/>
       <c r="AD140" t="inlineStr"/>
       <c r="AE140" t="inlineStr"/>
-      <c r="AF140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>Metro of Bogota First Line - First tranch</t>
+        </is>
+      </c>
       <c r="AG140" t="inlineStr"/>
-      <c r="AH140" t="inlineStr"/>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr"/>
-      <c r="AK140" t="inlineStr"/>
-      <c r="AL140" t="inlineStr"/>
-      <c r="AM140" t="inlineStr"/>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>Metro of Bogota First Line - First tranch</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -19179,29 +17787,21 @@
       </c>
       <c r="Y141" t="inlineStr"/>
       <c r="Z141" t="inlineStr"/>
-      <c r="AA141" t="inlineStr"/>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr"/>
       <c r="AD141" t="inlineStr"/>
       <c r="AE141" t="inlineStr"/>
-      <c r="AF141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>Segment Montero-Yapacaní from the double lane in the road Santa Cruz-Cochabamba</t>
+        </is>
+      </c>
       <c r="AG141" t="inlineStr"/>
-      <c r="AH141" t="inlineStr"/>
-      <c r="AI141" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ141" t="inlineStr"/>
-      <c r="AK141" t="inlineStr"/>
-      <c r="AL141" t="inlineStr"/>
-      <c r="AM141" t="inlineStr"/>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>Segment Montero-Yapacaní from the double lane in the road Santa Cruz-Cochabamba</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -19302,29 +17902,21 @@
       </c>
       <c r="Y142" t="inlineStr"/>
       <c r="Z142" t="inlineStr"/>
-      <c r="AA142" t="inlineStr"/>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr"/>
       <c r="AD142" t="inlineStr"/>
       <c r="AE142" t="inlineStr"/>
-      <c r="AF142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>Multi-Phase Wastewater Rehabilitation Program- Phase I</t>
+        </is>
+      </c>
       <c r="AG142" t="inlineStr"/>
-      <c r="AH142" t="inlineStr"/>
-      <c r="AI142" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ142" t="inlineStr"/>
-      <c r="AK142" t="inlineStr"/>
-      <c r="AL142" t="inlineStr"/>
-      <c r="AM142" t="inlineStr"/>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>Multi-Phase Wastewater Rehabilitation Program- Phase I</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -19425,29 +18017,21 @@
       </c>
       <c r="Y143" t="inlineStr"/>
       <c r="Z143" t="inlineStr"/>
-      <c r="AA143" t="inlineStr"/>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="inlineStr"/>
       <c r="AD143" t="inlineStr"/>
       <c r="AE143" t="inlineStr"/>
-      <c r="AF143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>Rehabilitation of Units 1 to 6 of Powerhouse I Simón Bolivar Hydroelectric Plant</t>
+        </is>
+      </c>
       <c r="AG143" t="inlineStr"/>
-      <c r="AH143" t="inlineStr"/>
-      <c r="AI143" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ143" t="inlineStr"/>
-      <c r="AK143" t="inlineStr"/>
-      <c r="AL143" t="inlineStr"/>
-      <c r="AM143" t="inlineStr"/>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>Rehabilitation of Units 1 to 6 of Powerhouse I Simón Bolivar Hydroelectric Plant</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -19548,29 +18132,21 @@
       </c>
       <c r="Y144" t="inlineStr"/>
       <c r="Z144" t="inlineStr"/>
-      <c r="AA144" t="inlineStr"/>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB144" t="inlineStr"/>
       <c r="AC144" t="inlineStr"/>
       <c r="AD144" t="inlineStr"/>
       <c r="AE144" t="inlineStr"/>
-      <c r="AF144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>The Bahamas Water Supply and Sanitation Systems Upgrade Program</t>
+        </is>
+      </c>
       <c r="AG144" t="inlineStr"/>
-      <c r="AH144" t="inlineStr"/>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr"/>
-      <c r="AK144" t="inlineStr"/>
-      <c r="AL144" t="inlineStr"/>
-      <c r="AM144" t="inlineStr"/>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>The Bahamas Water Supply and Sanitation Systems Upgrade Program</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -19671,29 +18247,21 @@
       </c>
       <c r="Y145" t="inlineStr"/>
       <c r="Z145" t="inlineStr"/>
-      <c r="AA145" t="inlineStr"/>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB145" t="inlineStr"/>
       <c r="AC145" t="inlineStr"/>
       <c r="AD145" t="inlineStr"/>
       <c r="AE145" t="inlineStr"/>
-      <c r="AF145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>Foreign Investment and Export Promotion Program</t>
+        </is>
+      </c>
       <c r="AG145" t="inlineStr"/>
-      <c r="AH145" t="inlineStr"/>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr"/>
-      <c r="AK145" t="inlineStr"/>
-      <c r="AL145" t="inlineStr"/>
-      <c r="AM145" t="inlineStr"/>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>Foreign Investment and Export Promotion Program</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -19794,29 +18362,21 @@
       </c>
       <c r="Y146" t="inlineStr"/>
       <c r="Z146" t="inlineStr"/>
-      <c r="AA146" t="inlineStr"/>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="AB146" t="inlineStr"/>
       <c r="AC146" t="inlineStr"/>
       <c r="AD146" t="inlineStr"/>
       <c r="AE146" t="inlineStr"/>
-      <c r="AF146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>Security Strengthening Project</t>
+        </is>
+      </c>
       <c r="AG146" t="inlineStr"/>
-      <c r="AH146" t="inlineStr"/>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ146" t="inlineStr"/>
-      <c r="AK146" t="inlineStr"/>
-      <c r="AL146" t="inlineStr"/>
-      <c r="AM146" t="inlineStr"/>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>Security Strengthening Project</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
